--- a/Initial_Datasets/Maya_Initial_Dataset/nfl_media.xlsx
+++ b/Initial_Datasets/Maya_Initial_Dataset/nfl_media.xlsx
@@ -1,17 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0cda40b4865d4573/Programming_Hub/is310/is310-group1/is310-spring-2026-group-1/Initial_Datasets/Maya_Initial_Dataset/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="114" documentId="11_0454703CEEEDAF8C972A80539CA0841841B7CAE8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A909B0D8-32CA-41C9-87A8-471F161B51F2}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="403">
   <si>
     <t>ID</t>
   </si>
@@ -429,16 +451,18 @@
   <si>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
       </rPr>
       <t xml:space="preserve">FS1's </t>
     </r>
     <r>
       <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
       </rPr>
       <t>The Herd with Colin Cowherd</t>
     </r>
@@ -749,23 +773,26 @@
   <si>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
       </rPr>
       <t xml:space="preserve">Wilson promoted the </t>
     </r>
     <r>
       <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
       </rPr>
       <t>TNF</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
       </rPr>
       <t xml:space="preserve">'s movement to Prime Video by showing off a "new ball" for 2022 with a catch phrase "Let's Ride" which has been a meme. </t>
     </r>
@@ -1027,27 +1054,282 @@
   </si>
   <si>
     <t>NBC Sports, Fox News</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>https://www.yahoo.com/entertainment/articles/jason-kelce-slammed-tone-deaf-185134012.html?guccounter=1&amp;guce_referrer=aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS8&amp;guce_referrer_sig=AQAAADrJ-a3_k8kxNkzivlOGOq4_OpPORRdt9NRY3butbKPSUleZi7xL_a7b1fWzsvaGTU1bZhVKP-hvn1HmMsM-ecLzFUapnrU_v-oNJ5Jv0xdPWjX5syumoNeUScHJ2CJ3Nj-Qvp_VFE1xaSkgYNGblNYtSfj_azVwJm3skuK1pOAc</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/articles/nfl-legend-warren-sapp-calls-154715384.html</t>
+  </si>
+  <si>
+    <t>https://www.cnn.com/2025/12/18/sport/football-nfl-rams-puka-nacua-apology-antisemitism</t>
+  </si>
+  <si>
+    <t>https://www.yahoo.com/entertainment/articles/travis-kelce-resurfaced-easter-tweet-123536254.html</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/article/deion-sanders-eats-crow-shedeur-175135709.html</t>
+  </si>
+  <si>
+    <t>https://www.outkick.com/sports/sports-media-silent-on-rashard-mendenhall-anti-white-tweet-calls-for-neo-segregation-bobby-burack</t>
+  </si>
+  <si>
+    <t>https://www.indystar.com/story/sports/nfl/colts/2023/01/19/ex-indianapolis-colts-coach-tony-dungy-deletes-cat-litter-tweet/69820624007/?gnt-cfr=1&amp;gca-cat=p&amp;gca-uir=true&amp;gca-epti=z116418e1131xxv116418d--71--b--71--&amp;gca-ft=216&amp;gca-ds=sophi</t>
+  </si>
+  <si>
+    <t>https://patriotswire.usatoday.com/story/sports/nfl/patriots/2026/01/12/maxx-crosby-tweets-out-patriots-player-social-media-crazy/88138724007/</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/sports/us-sports/puka-nacua-twitter-post-slams-nfl-refs-after-la-rams-loss-as-wr-doubles-down-on-criticism-can-you-say-i-was-wrong-101766124227161.html</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/article/panthers-olb-princely-umanmielen-explains-195456186.html</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/article/ben-dinucci-needed-airport-beer-182105778.html</t>
+  </si>
+  <si>
+    <t>https://www.nfl.com/news/nfl-trailblazer-carl-nassib-made-enduring-impact-on-nonprofit-the-trevor-project</t>
+  </si>
+  <si>
+    <t>https://www.i24news.tv/en/news/international/sport/1596555425-former-nfl-player-larry-johnson-tweets-anti-semitic-tropes</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/nfl/story/_/id/33254443/washington-commanders-dt-jonathan-allen-apologizes-saying-dine-hitler</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/news/ni62461533/</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/rugby/story/_/id/29344948/former-nfl-punter-receives-roasting-rugby-players-dominate-tweet</t>
+  </si>
+  <si>
+    <t>https://www.yahoo.com/entertainment/celebrity/articles/nfl-robert-griffin-iii-stirs-173949328.html</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/articles/kyle-pitts-calls-teammates-fake-193445440.html</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/articles/shipped-off-piece-garbage-baker-130729364.html</t>
+  </si>
+  <si>
+    <t>https://www.usmagazine.com/entertainment/news/puka-nacuas-ex-shares-baby-pics-during-rams-game-after-paternity-fight/</t>
+  </si>
+  <si>
+    <t>https://www.yahoo.com/entertainment/celebrity/articles/former-nfl-player-taylor-lewan-180101452.html</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/articles/ex-nfl-player-critical-league-195849417.html</t>
+  </si>
+  <si>
+    <t>https://www.aol.com/articles/former-nfl-qb-ryan-leaf-230331087.html?guccounter=1&amp;guce_referrer=aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS8&amp;guce_referrer_sig=AQAAAKXEvsXD1LXyXgXjG7XQI8_Rmj8tlILgREZTvg0Tw0FPvatBElsL-rgP7uY5MMkb7hT8LkRAYcltB5f15jyPQVGsDyIeZ7iYLapgIiERTEAUw-dGvCk0hA8SqOmdnwYy5Q7MDOyxu3D_DOiuT4F9DQtYFRQTk0TwR6z536vsIatD</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/articles/travis-kelce-career-planned-nfl-130453202.html</t>
+  </si>
+  <si>
+    <t>https://people.com/vernon-davis-breaks-silence-on-allegations-he-attacked-pregnant-woman-11896782</t>
+  </si>
+  <si>
+    <t>https://www.aol.com/articles/former-nfl-quarterback-cam-newton-213948646.html</t>
+  </si>
+  <si>
+    <t>https://www.usmagazine.com/celebrity-news/news/tom-bradys-divorce-took-a-lot-out-of-me-during-his-last-nfl-season/</t>
+  </si>
+  <si>
+    <t>https://www.nfl.com/news/a-j-brown-let-frustrations-boil-over-in-cryptic-post-after-eagles-win-over-buccaneers</t>
+  </si>
+  <si>
+    <t>https://broncoswire.usatoday.com/story/sports/nfl/broncos/2026/03/20/broncos-liljordan-humphrey-jersey-number/89231245007/</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/article/amik-robertson-hilarious-reaction-aidan-225021132.html</t>
+  </si>
+  <si>
+    <t>https://www.nbcsports.com/nfl/profootballtalk/rumor-mill/news/j-k-dobbins-injured-his-foot-on-what-he-believes-was-a-hip-drop-tackle</t>
+  </si>
+  <si>
+    <t>https://www.usmagazine.com/celebrity-news/news/jason-kelce-deletes-tweet-mocking-giants-kicker-who-was-cut-from-team/</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/articles/emeka-egbuka-tweet-cte-real-203551445.html</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/articles/nfl-legend-does-not-approve-135615792.html</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/articles/caleb-williams-fires-back-packers-062855936.html</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/nfl/story/_/id/46932042/seattle-seahawks-cooper-kupp-return-los-angeles-rams-exit</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/nfl/story/_/id/35328432/cardinals-jj-watt-announces-final-nfl-season</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/nfl/article/saquon-barkley-defends-decision-to-golf-with-president-donald-trump-before-eagles-white-house-visit-154715971.html</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/articles/joe-burrow-just-tweeted-first-231704693.html</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/articles/patrick-mahomes-allen-lazards-playful-113300993.html</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/twitter-justin-jefferson-call-league-022609777.html</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/jonathan-owens-disappointed-podcast-comments-230735434.html</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/nfl-cam-newton-trash-talk-hs-football-player-social-media-calls-out-disrespect-im-rich-200142619.html</t>
+  </si>
+  <si>
+    <t>https://www.dailymail.com/sport/nfl/article-15666519/new-york-giants-cam-skattebo-cte.html</t>
+  </si>
+  <si>
+    <t>https://www.msn.com/en-us/sports/nfl/a-new-chapter-49ers-rb-christian-mccaffrey-and-olivia-culpo-welcome-baby-girl/ar-AA1IwK2q?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+  </si>
+  <si>
+    <t>https://nypost.com/2026/03/20/sports/former-pro-bowl-wideout-dj-chark-retires-from-nfl-at-29/</t>
+  </si>
+  <si>
+    <t>https://www.foxnews.com/sports/antonio-brown-sends-bizarre-tweet-claiming-he-will-end-retirement-play-ravens</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/articles/tyreek-hill-posts-cryptic-message-205109662.html</t>
+  </si>
+  <si>
+    <t>https://www.nfl.com/news/dolphins-tua-tagovailoa-calls-out-attendance-at-players-only-meetings-following-loss-to-chargers</t>
+  </si>
+  <si>
+    <t>https://www.nfl.com/news/bills-josh-allen-laments-playoff-loss-broncos-let-my-teammates-down</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/articles/bills-locker-room-back-qb-144533874.html</t>
+  </si>
+  <si>
+    <t>https://www.foxnews.com/sports/ex-nfl-star-shawne-merriman-advocating-players-get-paid-more-when-tv-rights-deals-explode</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/russell-wilson-promotes-amazon-thursday-120024789.html</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/article/patrick-mahomes-sparks-controversy-talking-211552277.html</t>
+  </si>
+  <si>
+    <t>https://www.cbsnews.com/news/harrison-butker-commencement-speech-abortion-pride-month-biden-diabolic-lies-told-women/</t>
+  </si>
+  <si>
+    <t>https://www.cnn.com/2020/07/07/us/desean-jackson-eagles-antisemitic-post-trnd</t>
+  </si>
+  <si>
+    <t>https://people.com/travis-kelce-says-it-s-a-great-honor-to-have-trump-at-super-bowl-8786317</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/articles/cam-akers-says-aaron-donald-142026159.html</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/articles/deandre-hopkins-addresses-wanting-ravens-190932304.html</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/articles/deandre-hopkins-airs-frustrations-ravens-020617578.html</t>
+  </si>
+  <si>
+    <t>https://www.usatoday.com/story/sports/nfl/2024/11/03/michael-thomas-derek-carr-twitter-x-saints/76032365007/</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/buffalo-bills-cole-beasley-calls-nflpa-a-joke-new-covid19-coronavirus-rules-restricting-unvaccinated-players-193720432.html</t>
+  </si>
+  <si>
+    <t>https://www.si.com/nfl/bengals/onsi/allbengals-insiders-plus/logan-wilson-comments-on-controversial-super-bowl-pass-interference-following-nfl-retirment-01km3qjx24q2</t>
+  </si>
+  <si>
+    <t>https://heavy.com/sports/nfl/buffalo-bills/stefon-diggs-nfl-draft-tweet/</t>
+  </si>
+  <si>
+    <t>https://www.cbsnews.com/news/damar-hamlin-first-public-comments-cardiac-arrest-buffalo-bills/</t>
+  </si>
+  <si>
+    <t>https://www.cincinnati.com/story/sports/nfl/bengals/2023/01/05/josh-allen-people-should-not-be-attacking-tee-higgins-whatsoever-as-damar-hamlin-recovers-cincinnati/69782959007/?gnt-cfr=1&amp;gca-cat=p&amp;gca-uir=true&amp;gca-epti=z115240e1162xxv115240d--58--b--58--&amp;gca-ft=200&amp;gca-ds=sophi</t>
+  </si>
+  <si>
+    <t>https://www.foxnews.com/sports/chiefs-travis-kelce-asks-reporters-why-you-guys-leaning-whole-ref-thing</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/nfl/story/_/id/34390654/cleveland-browns-deshaun-watson-interview-apologizes-all-women-impacted-situation</t>
+  </si>
+  <si>
+    <t>https://nypost.com/2025/04/18/sports/kadarius-toney-responds-after-retirement-rumors-run-wild/</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/nfl/story/_/id/39633369/mecole-hardman-denies-leaking-jets-game-plans-chiefs-eagles</t>
+  </si>
+  <si>
+    <t>https://www.nytimes.com/athletic/2058072/2020/09/10/it-saves-lives-dak-prescott-opens-up-on-mental-health-value-of-transparency/</t>
+  </si>
+  <si>
+    <t>https://ninerswire.usatoday.com/story/sports/nfl/niners/2024/01/30/george-kittle-49ers-comeback-nfc-championship-had-us-in-the-first-half/79537007007/</t>
+  </si>
+  <si>
+    <t>https://www.nfl.com/news/aaron-rodgers-full-responsibility-misleading-comments-covid-19-vaccine</t>
+  </si>
+  <si>
+    <t>https://sports.yahoo.com/article/ceedee-lamb-tells-jerry-jones-190837198.html</t>
+  </si>
+  <si>
+    <t>https://www.nfl.com/news/bears-qb-justin-fields-clarifies-robotic-comments-i-m-not-blaming-anything-on-th</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1056,55 +1338,62 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1294,22 +1583,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O264"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="6" max="6" width="15.0"/>
-    <col customWidth="1" min="10" max="10" width="13.88"/>
-    <col customWidth="1" min="12" max="12" width="14.63"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="10" max="10" width="13.90625" customWidth="1"/>
+    <col min="12" max="12" width="14.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1346,10 +1638,13 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2">
+      <c r="M1" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>12</v>
@@ -1358,9 +1653,9 @@
         <v>13</v>
       </c>
       <c r="D2" s="1">
-        <v>2025.0</v>
-      </c>
-      <c r="E2" s="1" t="s">
+        <v>2025</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -1384,10 +1679,15 @@
       <c r="L2" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3">
+      <c r="M2" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+    </row>
+    <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>22</v>
@@ -1396,15 +1696,15 @@
         <v>13</v>
       </c>
       <c r="D3" s="1">
-        <v>2025.0</v>
-      </c>
-      <c r="E3" s="1" t="s">
+        <v>2025</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -1422,10 +1722,15 @@
       <c r="L3" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4">
+      <c r="M3" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+    </row>
+    <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>29</v>
@@ -1434,7 +1739,7 @@
         <v>30</v>
       </c>
       <c r="D4" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>31</v>
@@ -1460,10 +1765,15 @@
       <c r="L4" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="5">
+      <c r="M4" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+    </row>
+    <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>35</v>
@@ -1472,7 +1782,7 @@
         <v>36</v>
       </c>
       <c r="D5" s="1">
-        <v>2024.0</v>
+        <v>2024</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>37</v>
@@ -1498,10 +1808,15 @@
       <c r="L5" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="6">
+      <c r="M5" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>41</v>
@@ -1510,7 +1825,7 @@
         <v>30</v>
       </c>
       <c r="D6" s="1">
-        <v>2024.0</v>
+        <v>2024</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>42</v>
@@ -1533,13 +1848,18 @@
       <c r="K6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="7">
+      <c r="M6" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>45</v>
@@ -1548,7 +1868,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="1">
-        <v>2023.0</v>
+        <v>2023</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>46</v>
@@ -1574,10 +1894,15 @@
       <c r="L7" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="8">
+      <c r="M7" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+    </row>
+    <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>49</v>
@@ -1586,7 +1911,7 @@
         <v>13</v>
       </c>
       <c r="D8" s="1">
-        <v>2023.0</v>
+        <v>2023</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>50</v>
@@ -1612,10 +1937,15 @@
       <c r="L8" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="9">
+      <c r="M8" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+    </row>
+    <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>53</v>
@@ -1624,7 +1954,7 @@
         <v>30</v>
       </c>
       <c r="D9" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>54</v>
@@ -1650,10 +1980,15 @@
       <c r="L9" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="10">
+      <c r="M9" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+    </row>
+    <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>29</v>
@@ -1662,7 +1997,7 @@
         <v>30</v>
       </c>
       <c r="D10" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>60</v>
@@ -1685,13 +2020,18 @@
       <c r="K10" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="L10" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="M10" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>64</v>
@@ -1700,7 +2040,7 @@
         <v>30</v>
       </c>
       <c r="D11" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>65</v>
@@ -1726,10 +2066,15 @@
       <c r="L11" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="12">
+      <c r="M11" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+    </row>
+    <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>69</v>
@@ -1738,7 +2083,7 @@
         <v>30</v>
       </c>
       <c r="D12" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>70</v>
@@ -1764,10 +2109,15 @@
       <c r="L12" s="1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="13">
+      <c r="M12" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+    </row>
+    <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>73</v>
@@ -1776,9 +2126,9 @@
         <v>30</v>
       </c>
       <c r="D13" s="1">
-        <v>2022.0</v>
-      </c>
-      <c r="E13" s="1" t="s">
+        <v>2022</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>74</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -1802,10 +2152,15 @@
       <c r="L13" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="14">
+      <c r="M13" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+    </row>
+    <row r="14" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>79</v>
@@ -1814,7 +2169,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="1">
-        <v>2020.0</v>
+        <v>2020</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>80</v>
@@ -1837,13 +2192,18 @@
       <c r="K14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="L14" s="4" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="15">
+      <c r="M14" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+    </row>
+    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>83</v>
@@ -1852,7 +2212,7 @@
         <v>30</v>
       </c>
       <c r="D15" s="1">
-        <v>2022.0</v>
+        <v>2022</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>84</v>
@@ -1875,13 +2235,18 @@
       <c r="K15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="L15" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="16">
+      <c r="M15" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+    </row>
+    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>87</v>
@@ -1890,7 +2255,7 @@
         <v>30</v>
       </c>
       <c r="D16" s="1">
-        <v>2019.0</v>
+        <v>2019</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>88</v>
@@ -1916,10 +2281,15 @@
       <c r="L16" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="17">
+      <c r="M16" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+    </row>
+    <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>91</v>
@@ -1928,7 +2298,7 @@
         <v>30</v>
       </c>
       <c r="D17" s="1">
-        <v>2020.0</v>
+        <v>2020</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>92</v>
@@ -1954,10 +2324,15 @@
       <c r="L17" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="18">
+      <c r="M17" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+    </row>
+    <row r="18" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>94</v>
@@ -1966,7 +2341,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>95</v>
@@ -1989,13 +2364,18 @@
       <c r="K18" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="L18" s="3" t="s">
+      <c r="L18" s="4" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="19">
+      <c r="M18" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+    </row>
+    <row r="19" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>98</v>
@@ -2004,7 +2384,7 @@
         <v>30</v>
       </c>
       <c r="D19" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>99</v>
@@ -2027,13 +2407,18 @@
       <c r="K19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L19" s="3" t="s">
+      <c r="L19" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="20">
+      <c r="M19" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+    </row>
+    <row r="20" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>103</v>
@@ -2042,7 +2427,7 @@
         <v>30</v>
       </c>
       <c r="D20" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>104</v>
@@ -2065,13 +2450,18 @@
       <c r="K20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="L20" s="4" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="21">
+      <c r="M20" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+    </row>
+    <row r="21" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>29</v>
@@ -2080,7 +2470,7 @@
         <v>30</v>
       </c>
       <c r="D21" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>106</v>
@@ -2103,13 +2493,18 @@
       <c r="K21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="L21" s="4" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="22">
+      <c r="M21" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+    </row>
+    <row r="22" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>111</v>
@@ -2118,7 +2513,7 @@
         <v>13</v>
       </c>
       <c r="D22" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>112</v>
@@ -2141,13 +2536,18 @@
       <c r="K22" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="L22" s="4" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="23">
+      <c r="M22" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+    </row>
+    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>114</v>
@@ -2156,7 +2556,7 @@
         <v>13</v>
       </c>
       <c r="D23" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>115</v>
@@ -2179,13 +2579,18 @@
       <c r="K23" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="L23" s="4" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="24">
+      <c r="M23" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+    </row>
+    <row r="24" spans="1:15" ht="362.5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>117</v>
@@ -2194,7 +2599,7 @@
         <v>13</v>
       </c>
       <c r="D24" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>118</v>
@@ -2217,22 +2622,27 @@
       <c r="K24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="L24" s="4" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="25">
+      <c r="M24" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+    </row>
+    <row r="25" spans="1:15" ht="125" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="B25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D25" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>121</v>
@@ -2258,10 +2668,15 @@
       <c r="L25" s="1" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="26">
+      <c r="M25" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+    </row>
+    <row r="26" spans="1:15" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>126</v>
@@ -2270,7 +2685,7 @@
         <v>13</v>
       </c>
       <c r="D26" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>127</v>
@@ -2293,13 +2708,18 @@
       <c r="K26" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="L26" s="4" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="27">
+      <c r="M26" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+    </row>
+    <row r="27" spans="1:15" ht="137.5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>130</v>
@@ -2308,7 +2728,7 @@
         <v>13</v>
       </c>
       <c r="D27" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>131</v>
@@ -2334,10 +2754,15 @@
       <c r="L27" s="1" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="28">
+      <c r="M27" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7"/>
+    </row>
+    <row r="28" spans="1:15" ht="138" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>135</v>
@@ -2346,7 +2771,7 @@
         <v>13</v>
       </c>
       <c r="D28" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>136</v>
@@ -2369,13 +2794,18 @@
       <c r="K28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L28" s="4" t="s">
+      <c r="L28" s="8" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="29">
+      <c r="M28" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
+    </row>
+    <row r="29" spans="1:15" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>140</v>
@@ -2384,7 +2814,7 @@
         <v>30</v>
       </c>
       <c r="D29" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>141</v>
@@ -2407,13 +2837,18 @@
       <c r="K29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="L29" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="30">
+      <c r="M29" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
+    </row>
+    <row r="30" spans="1:15" ht="137.5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>144</v>
@@ -2422,7 +2857,7 @@
         <v>30</v>
       </c>
       <c r="D30" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>145</v>
@@ -2448,10 +2883,15 @@
       <c r="L30" s="1" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="31">
+      <c r="M30" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="N30" s="7"/>
+      <c r="O30" s="7"/>
+    </row>
+    <row r="31" spans="1:15" ht="137.5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>148</v>
@@ -2460,7 +2900,7 @@
         <v>30</v>
       </c>
       <c r="D31" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>149</v>
@@ -2486,10 +2926,15 @@
       <c r="L31" s="1" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="32">
+      <c r="M31" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+    </row>
+    <row r="32" spans="1:15" ht="137.5" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>152</v>
@@ -2498,7 +2943,7 @@
         <v>30</v>
       </c>
       <c r="D32" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>153</v>
@@ -2524,10 +2969,15 @@
       <c r="L32" s="1" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="33">
+      <c r="M32" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+    </row>
+    <row r="33" spans="1:15" ht="125" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
@@ -2536,7 +2986,7 @@
         <v>13</v>
       </c>
       <c r="D33" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>155</v>
@@ -2562,10 +3012,15 @@
       <c r="L33" s="1" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="34">
+      <c r="M33" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+    </row>
+    <row r="34" spans="1:15" ht="87.5" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>158</v>
@@ -2574,7 +3029,7 @@
         <v>30</v>
       </c>
       <c r="D34" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>159</v>
@@ -2600,10 +3055,15 @@
       <c r="L34" s="1" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="35">
+      <c r="M34" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+    </row>
+    <row r="35" spans="1:15" ht="100" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>162</v>
@@ -2612,7 +3072,7 @@
         <v>13</v>
       </c>
       <c r="D35" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>163</v>
@@ -2635,13 +3095,18 @@
       <c r="K35" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L35" s="4" t="s">
+      <c r="L35" s="3" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="36">
+      <c r="M35" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="N35" s="7"/>
+      <c r="O35" s="7"/>
+    </row>
+    <row r="36" spans="1:15" ht="87.5" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>166</v>
@@ -2650,7 +3115,7 @@
         <v>30</v>
       </c>
       <c r="D36" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>167</v>
@@ -2676,19 +3141,24 @@
       <c r="L36" s="1" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="37">
+      <c r="M36" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="N36" s="7"/>
+      <c r="O36" s="7"/>
+    </row>
+    <row r="37" spans="1:15" ht="137.5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>36.0</v>
-      </c>
-      <c r="B37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>170</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D37" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>171</v>
@@ -2714,10 +3184,15 @@
       <c r="L37" s="1" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="38">
+      <c r="M37" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="N37" s="7"/>
+      <c r="O37" s="7"/>
+    </row>
+    <row r="38" spans="1:15" ht="100" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>174</v>
@@ -2726,7 +3201,7 @@
         <v>13</v>
       </c>
       <c r="D38" s="1">
-        <v>2022.0</v>
+        <v>2022</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>175</v>
@@ -2752,10 +3227,15 @@
       <c r="L38" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="39">
+      <c r="M38" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
+    </row>
+    <row r="39" spans="1:15" ht="175" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>177</v>
@@ -2764,7 +3244,7 @@
         <v>30</v>
       </c>
       <c r="D39" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>178</v>
@@ -2790,10 +3270,15 @@
       <c r="L39" s="1" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="40">
+      <c r="M39" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="N39" s="7"/>
+      <c r="O39" s="7"/>
+    </row>
+    <row r="40" spans="1:15" ht="200" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>181</v>
@@ -2802,7 +3287,7 @@
         <v>30</v>
       </c>
       <c r="D40" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>182</v>
@@ -2828,10 +3313,15 @@
       <c r="L40" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="41">
+      <c r="M40" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="N40" s="7"/>
+      <c r="O40" s="7"/>
+    </row>
+    <row r="41" spans="1:15" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>184</v>
@@ -2840,7 +3330,7 @@
         <v>30</v>
       </c>
       <c r="D41" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>185</v>
@@ -2866,10 +3356,15 @@
       <c r="L41" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="42">
+      <c r="M41" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="N41" s="7"/>
+      <c r="O41" s="7"/>
+    </row>
+    <row r="42" spans="1:15" ht="87.5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>187</v>
@@ -2878,7 +3373,7 @@
         <v>30</v>
       </c>
       <c r="D42" s="1">
-        <v>2024.0</v>
+        <v>2024</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>188</v>
@@ -2904,10 +3399,15 @@
       <c r="L42" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="43">
+      <c r="M42" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="N42" s="7"/>
+      <c r="O42" s="7"/>
+    </row>
+    <row r="43" spans="1:15" ht="137.5" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>190</v>
@@ -2916,7 +3416,7 @@
         <v>30</v>
       </c>
       <c r="D43" s="1">
-        <v>2024.0</v>
+        <v>2024</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>191</v>
@@ -2942,10 +3442,15 @@
       <c r="L43" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="44">
+      <c r="M43" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="N43" s="7"/>
+      <c r="O43" s="7"/>
+    </row>
+    <row r="44" spans="1:15" ht="187.5" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>130</v>
@@ -2954,7 +3459,7 @@
         <v>13</v>
       </c>
       <c r="D44" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>195</v>
@@ -2980,10 +3485,15 @@
       <c r="L44" s="1" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="45">
+      <c r="M44" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="N44" s="7"/>
+      <c r="O44" s="7"/>
+    </row>
+    <row r="45" spans="1:15" ht="100" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>199</v>
@@ -2992,7 +3502,7 @@
         <v>30</v>
       </c>
       <c r="D45" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>200</v>
@@ -3018,10 +3528,15 @@
       <c r="L45" s="1" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="46">
+      <c r="M45" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="N45" s="7"/>
+      <c r="O45" s="7"/>
+    </row>
+    <row r="46" spans="1:15" ht="262.5" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>204</v>
@@ -3030,7 +3545,7 @@
         <v>30</v>
       </c>
       <c r="D46" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>205</v>
@@ -3056,10 +3571,15 @@
       <c r="L46" s="1" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="47">
+      <c r="M46" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="N46" s="7"/>
+      <c r="O46" s="7"/>
+    </row>
+    <row r="47" spans="1:15" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>208</v>
@@ -3068,7 +3588,7 @@
         <v>13</v>
       </c>
       <c r="D47" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>209</v>
@@ -3094,10 +3614,15 @@
       <c r="L47" s="1" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="48">
+      <c r="M47" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="N47" s="7"/>
+      <c r="O47" s="7"/>
+    </row>
+    <row r="48" spans="1:15" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>212</v>
@@ -3106,7 +3631,7 @@
         <v>13</v>
       </c>
       <c r="D48" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>213</v>
@@ -3120,22 +3645,27 @@
       <c r="H48" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I48" s="2" t="s">
+      <c r="I48" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J48" s="2" t="s">
+      <c r="J48" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K48" s="2" t="s">
+      <c r="K48" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="L48" s="2" t="s">
+      <c r="L48" s="4" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="49">
+      <c r="M48" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="N48" s="7"/>
+      <c r="O48" s="7"/>
+    </row>
+    <row r="49" spans="1:15" ht="100" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>216</v>
@@ -3144,7 +3674,7 @@
         <v>30</v>
       </c>
       <c r="D49" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>217</v>
@@ -3158,22 +3688,27 @@
       <c r="H49" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I49" s="2" t="s">
+      <c r="I49" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J49" s="2" t="s">
+      <c r="J49" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K49" s="2" t="s">
+      <c r="K49" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L49" s="2" t="s">
+      <c r="L49" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="50">
+      <c r="M49" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="N49" s="7"/>
+      <c r="O49" s="7"/>
+    </row>
+    <row r="50" spans="1:15" ht="137.5" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>219</v>
@@ -3182,7 +3717,7 @@
         <v>30</v>
       </c>
       <c r="D50" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>220</v>
@@ -3196,22 +3731,27 @@
       <c r="H50" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I50" s="2" t="s">
+      <c r="I50" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J50" s="2" t="s">
+      <c r="J50" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K50" s="2" t="s">
+      <c r="K50" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="L50" s="2" t="s">
+      <c r="L50" s="1" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="51">
+      <c r="M50" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="N50" s="7"/>
+      <c r="O50" s="7"/>
+    </row>
+    <row r="51" spans="1:15" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>224</v>
@@ -3220,7 +3760,7 @@
         <v>30</v>
       </c>
       <c r="D51" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>225</v>
@@ -3246,10 +3786,15 @@
       <c r="L51" s="1" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="52">
+      <c r="M51" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="N51" s="7"/>
+      <c r="O51" s="7"/>
+    </row>
+    <row r="52" spans="1:15" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>51.0</v>
+        <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>229</v>
@@ -3258,7 +3803,7 @@
         <v>30</v>
       </c>
       <c r="D52" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>230</v>
@@ -3284,10 +3829,15 @@
       <c r="L52" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="53">
+      <c r="M52" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="N52" s="7"/>
+      <c r="O52" s="7"/>
+    </row>
+    <row r="53" spans="1:15" ht="137.5" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>233</v>
@@ -3296,7 +3846,7 @@
         <v>13</v>
       </c>
       <c r="D53" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>234</v>
@@ -3322,10 +3872,15 @@
       <c r="L53" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="54">
+      <c r="M53" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="N53" s="7"/>
+      <c r="O53" s="7"/>
+    </row>
+    <row r="54" spans="1:15" ht="138" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>238</v>
@@ -3334,7 +3889,7 @@
         <v>30</v>
       </c>
       <c r="D54" s="1">
-        <v>2022.0</v>
+        <v>2022</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>239</v>
@@ -3357,13 +3912,18 @@
       <c r="K54" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L54" s="3" t="s">
+      <c r="L54" s="1" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="55">
+      <c r="M54" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="N54" s="7"/>
+      <c r="O54" s="7"/>
+    </row>
+    <row r="55" spans="1:15" ht="137.5" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>54.0</v>
+        <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>184</v>
@@ -3372,7 +3932,7 @@
         <v>30</v>
       </c>
       <c r="D55" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>242</v>
@@ -3398,10 +3958,15 @@
       <c r="L55" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="56">
+      <c r="M55" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="N55" s="7"/>
+      <c r="O55" s="7"/>
+    </row>
+    <row r="56" spans="1:15" ht="162.5" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>245</v>
@@ -3410,7 +3975,7 @@
         <v>30</v>
       </c>
       <c r="D56" s="1">
-        <v>2024.0</v>
+        <v>2024</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>246</v>
@@ -3436,10 +4001,15 @@
       <c r="L56" s="1" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="57">
+      <c r="M56" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="N56" s="7"/>
+      <c r="O56" s="7"/>
+    </row>
+    <row r="57" spans="1:15" ht="137.5" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>250</v>
@@ -3448,7 +4018,7 @@
         <v>30</v>
       </c>
       <c r="D57" s="1">
-        <v>2020.0</v>
+        <v>2020</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>251</v>
@@ -3474,10 +4044,15 @@
       <c r="L57" s="1" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="58">
+      <c r="M57" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="N57" s="7"/>
+      <c r="O57" s="7"/>
+    </row>
+    <row r="58" spans="1:15" ht="125" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>57.0</v>
+        <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>35</v>
@@ -3486,7 +4061,7 @@
         <v>30</v>
       </c>
       <c r="D58" s="1">
-        <v>2024.0</v>
+        <v>2024</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>254</v>
@@ -3512,10 +4087,15 @@
       <c r="L58" s="1" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="59">
+      <c r="M58" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="N58" s="7"/>
+      <c r="O58" s="7"/>
+    </row>
+    <row r="59" spans="1:15" ht="175" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>258</v>
@@ -3524,7 +4104,7 @@
         <v>30</v>
       </c>
       <c r="D59" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>259</v>
@@ -3550,10 +4130,15 @@
       <c r="L59" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="60">
+      <c r="M59" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="N59" s="7"/>
+      <c r="O59" s="7"/>
+    </row>
+    <row r="60" spans="1:15" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>59.0</v>
+        <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>261</v>
@@ -3562,7 +4147,7 @@
         <v>30</v>
       </c>
       <c r="D60" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>262</v>
@@ -3588,10 +4173,15 @@
       <c r="L60" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="61">
+      <c r="M60" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="N60" s="7"/>
+      <c r="O60" s="7"/>
+    </row>
+    <row r="61" spans="1:15" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>261</v>
@@ -3600,7 +4190,7 @@
         <v>30</v>
       </c>
       <c r="D61" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>264</v>
@@ -3626,19 +4216,24 @@
       <c r="L61" s="1" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="62">
+      <c r="M61" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="N61" s="7"/>
+      <c r="O61" s="7"/>
+    </row>
+    <row r="62" spans="1:15" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>61.0</v>
-      </c>
-      <c r="B62" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" s="4" t="s">
         <v>267</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D62" s="1">
-        <v>2024.0</v>
+        <v>2024</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>268</v>
@@ -3664,10 +4259,15 @@
       <c r="L62" s="1" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="63">
+      <c r="M62" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="N62" s="7"/>
+      <c r="O62" s="7"/>
+    </row>
+    <row r="63" spans="1:15" ht="162.5" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>62.0</v>
+        <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>271</v>
@@ -3676,7 +4276,7 @@
         <v>30</v>
       </c>
       <c r="D63" s="1">
-        <v>2021.0</v>
+        <v>2021</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>272</v>
@@ -3702,10 +4302,15 @@
       <c r="L63" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="64">
+      <c r="M63" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="N63" s="7"/>
+      <c r="O63" s="7"/>
+    </row>
+    <row r="64" spans="1:15" ht="175" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>274</v>
@@ -3714,7 +4319,7 @@
         <v>13</v>
       </c>
       <c r="D64" s="1">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>275</v>
@@ -3740,10 +4345,15 @@
       <c r="L64" s="1" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="65">
+      <c r="M64" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="N64" s="7"/>
+      <c r="O64" s="7"/>
+    </row>
+    <row r="65" spans="1:15" ht="87.5" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>277</v>
@@ -3752,7 +4362,7 @@
         <v>30</v>
       </c>
       <c r="D65" s="1">
-        <v>2023.0</v>
+        <v>2023</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>278</v>
@@ -3775,13 +4385,18 @@
       <c r="K65" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="L65" s="1" t="s">
+      <c r="L65" s="4" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="66">
+      <c r="M65" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="N65" s="7"/>
+      <c r="O65" s="7"/>
+    </row>
+    <row r="66" spans="1:15" ht="137.5" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>281</v>
@@ -3790,7 +4405,7 @@
         <v>30</v>
       </c>
       <c r="D66" s="1">
-        <v>2023.0</v>
+        <v>2023</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>282</v>
@@ -3816,10 +4431,15 @@
       <c r="L66" s="1" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="67">
+      <c r="M66" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="N66" s="7"/>
+      <c r="O66" s="7"/>
+    </row>
+    <row r="67" spans="1:15" ht="300" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>66.0</v>
+        <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>224</v>
@@ -3828,7 +4448,7 @@
         <v>30</v>
       </c>
       <c r="D67" s="1">
-        <v>2023.0</v>
+        <v>2023</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>285</v>
@@ -3854,10 +4474,15 @@
       <c r="L67" s="1" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="68">
+      <c r="M67" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="N67" s="7"/>
+      <c r="O67" s="7"/>
+    </row>
+    <row r="68" spans="1:15" ht="137.5" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>67.0</v>
+        <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>35</v>
@@ -3866,7 +4491,7 @@
         <v>30</v>
       </c>
       <c r="D68" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>289</v>
@@ -3889,13 +4514,18 @@
       <c r="K68" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L68" s="5" t="s">
+      <c r="L68" s="3" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="69">
+      <c r="M68" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="N68" s="7"/>
+      <c r="O68" s="7"/>
+    </row>
+    <row r="69" spans="1:15" ht="150" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>292</v>
@@ -3904,7 +4534,7 @@
         <v>30</v>
       </c>
       <c r="D69" s="1">
-        <v>2022.0</v>
+        <v>2022</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>293</v>
@@ -3927,13 +4557,18 @@
       <c r="K69" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L69" s="3" t="s">
+      <c r="L69" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="70">
+      <c r="M69" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="N69" s="7"/>
+      <c r="O69" s="7"/>
+    </row>
+    <row r="70" spans="1:15" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>296</v>
@@ -3942,7 +4577,7 @@
         <v>297</v>
       </c>
       <c r="D70" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>298</v>
@@ -3965,13 +4600,18 @@
       <c r="K70" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L70" s="3" t="s">
+      <c r="L70" s="1" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="71">
+      <c r="M70" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="N70" s="7"/>
+      <c r="O70" s="7"/>
+    </row>
+    <row r="71" spans="1:15" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>301</v>
@@ -3980,7 +4620,7 @@
         <v>30</v>
       </c>
       <c r="D71" s="1">
-        <v>2024.0</v>
+        <v>2024</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>302</v>
@@ -4006,10 +4646,15 @@
       <c r="L71" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="72">
+      <c r="M71" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="N71" s="7"/>
+      <c r="O71" s="7"/>
+    </row>
+    <row r="72" spans="1:15" ht="125" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>304</v>
@@ -4018,7 +4663,7 @@
         <v>30</v>
       </c>
       <c r="D72" s="1">
-        <v>2020.0</v>
+        <v>2020</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>305</v>
@@ -4041,13 +4686,18 @@
       <c r="K72" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L72" s="3" t="s">
+      <c r="L72" s="1" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="73">
+      <c r="M72" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="N72" s="7"/>
+      <c r="O72" s="7"/>
+    </row>
+    <row r="73" spans="1:15" ht="162.5" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>72.0</v>
+        <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>309</v>
@@ -4056,7 +4706,7 @@
         <v>30</v>
       </c>
       <c r="D73" s="1">
-        <v>2024.0</v>
+        <v>2024</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>310</v>
@@ -4079,13 +4729,18 @@
       <c r="K73" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="L73" s="3" t="s">
+      <c r="L73" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="74">
+      <c r="M73" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="N73" s="7"/>
+      <c r="O73" s="7"/>
+    </row>
+    <row r="74" spans="1:15" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>73.0</v>
+        <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>314</v>
@@ -4094,7 +4749,7 @@
         <v>30</v>
       </c>
       <c r="D74" s="1">
-        <v>2021.0</v>
+        <v>2021</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>315</v>
@@ -4120,10 +4775,15 @@
       <c r="L74" s="1" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="75">
+      <c r="M74" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="N74" s="7"/>
+      <c r="O74" s="7"/>
+    </row>
+    <row r="75" spans="1:15" ht="87.5" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>74.0</v>
+        <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>319</v>
@@ -4132,7 +4792,7 @@
         <v>30</v>
       </c>
       <c r="D75" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>320</v>
@@ -4155,13 +4815,18 @@
       <c r="K75" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L75" s="3" t="s">
+      <c r="L75" s="4" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="76">
+      <c r="M75" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="N75" s="7"/>
+      <c r="O75" s="7"/>
+    </row>
+    <row r="76" spans="1:15" ht="200" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>322</v>
@@ -4170,7 +4835,7 @@
         <v>30</v>
       </c>
       <c r="D76" s="1">
-        <v>2023.0</v>
+        <v>2023</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>323</v>
@@ -4193,2467 +4858,2706 @@
       <c r="K76" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L76" s="1" t="s">
+      <c r="L76" s="4" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="77">
+      <c r="M76" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="N76" s="7"/>
+      <c r="O76" s="7"/>
+    </row>
+    <row r="77" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="6"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="6"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="6"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
       <c r="L77" s="1"/>
-    </row>
-    <row r="78">
+      <c r="M77" s="7"/>
+      <c r="N77" s="7"/>
+      <c r="O77" s="7"/>
+    </row>
+    <row r="78" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
       <c r="L78" s="1"/>
-    </row>
-    <row r="79">
+      <c r="M78" s="7"/>
+      <c r="N78" s="7"/>
+      <c r="O78" s="7"/>
+    </row>
+    <row r="79" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
-      <c r="J79" s="6"/>
-      <c r="K79" s="6"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
       <c r="L79" s="1"/>
-    </row>
-    <row r="80">
+      <c r="M79" s="7"/>
+      <c r="N79" s="7"/>
+      <c r="O79" s="7"/>
+    </row>
+    <row r="80" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="6"/>
-      <c r="F80" s="6"/>
-      <c r="G80" s="6"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="J80" s="6"/>
-      <c r="K80" s="6"/>
-      <c r="L80" s="6"/>
-    </row>
-    <row r="81">
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+      <c r="K80" s="1"/>
+      <c r="L80" s="1"/>
+      <c r="M80" s="7"/>
+      <c r="N80" s="7"/>
+      <c r="O80" s="7"/>
+    </row>
+    <row r="81" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
-      <c r="J81" s="6"/>
-      <c r="K81" s="6"/>
-      <c r="L81" s="6"/>
-    </row>
-    <row r="82">
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+      <c r="M81" s="7"/>
+      <c r="N81" s="7"/>
+      <c r="O81" s="7"/>
+    </row>
+    <row r="82" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="6"/>
-      <c r="J82" s="6"/>
-      <c r="K82" s="6"/>
-      <c r="L82" s="6"/>
-    </row>
-    <row r="83">
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+      <c r="M82" s="7"/>
+      <c r="N82" s="7"/>
+      <c r="O82" s="7"/>
+    </row>
+    <row r="83" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
-      <c r="B83" s="6"/>
-      <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="6"/>
-      <c r="F83" s="6"/>
-      <c r="G83" s="6"/>
-      <c r="H83" s="6"/>
-      <c r="I83" s="6"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6"/>
-      <c r="L83" s="6"/>
-    </row>
-    <row r="84">
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="L83" s="1"/>
+      <c r="M83" s="7"/>
+      <c r="N83" s="7"/>
+      <c r="O83" s="7"/>
+    </row>
+    <row r="84" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="6"/>
-      <c r="F84" s="6"/>
-      <c r="G84" s="6"/>
-      <c r="H84" s="6"/>
-      <c r="I84" s="6"/>
-      <c r="J84" s="6"/>
-      <c r="K84" s="6"/>
-      <c r="L84" s="6"/>
-    </row>
-    <row r="85">
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" s="1"/>
+      <c r="L84" s="1"/>
+      <c r="M84" s="7"/>
+      <c r="N84" s="7"/>
+      <c r="O84" s="7"/>
+    </row>
+    <row r="85" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="6"/>
-      <c r="I85" s="6"/>
-      <c r="J85" s="6"/>
-      <c r="K85" s="6"/>
-      <c r="L85" s="6"/>
-    </row>
-    <row r="86">
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="L85" s="1"/>
+      <c r="M85" s="7"/>
+      <c r="N85" s="7"/>
+      <c r="O85" s="7"/>
+    </row>
+    <row r="86" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="6"/>
-      <c r="F86" s="6"/>
-      <c r="G86" s="6"/>
-      <c r="H86" s="6"/>
-      <c r="I86" s="6"/>
-      <c r="J86" s="6"/>
-      <c r="K86" s="6"/>
-      <c r="L86" s="6"/>
-    </row>
-    <row r="87">
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="1"/>
+      <c r="M86" s="7"/>
+      <c r="N86" s="7"/>
+      <c r="O86" s="7"/>
+    </row>
+    <row r="87" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="6"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6"/>
-      <c r="L87" s="6"/>
-    </row>
-    <row r="88">
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
+      <c r="K87" s="1"/>
+      <c r="L87" s="1"/>
+      <c r="M87" s="7"/>
+      <c r="N87" s="7"/>
+      <c r="O87" s="7"/>
+    </row>
+    <row r="88" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
-      <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
-      <c r="G88" s="6"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-      <c r="J88" s="6"/>
-      <c r="K88" s="6"/>
-      <c r="L88" s="6"/>
-    </row>
-    <row r="89">
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
+      <c r="M88" s="7"/>
+      <c r="N88" s="7"/>
+      <c r="O88" s="7"/>
+    </row>
+    <row r="89" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
-      <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
-      <c r="I89" s="6"/>
-      <c r="J89" s="6"/>
-      <c r="L89" s="6"/>
-    </row>
-    <row r="90">
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
+      <c r="K89" s="5"/>
+      <c r="L89" s="1"/>
+      <c r="M89" s="7"/>
+      <c r="N89" s="7"/>
+      <c r="O89" s="7"/>
+    </row>
+    <row r="90" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="6"/>
-      <c r="F90" s="6"/>
-      <c r="G90" s="6"/>
-      <c r="H90" s="6"/>
-      <c r="I90" s="6"/>
-      <c r="J90" s="6"/>
-      <c r="L90" s="6"/>
-    </row>
-    <row r="91">
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+      <c r="K90" s="5"/>
+      <c r="L90" s="1"/>
+      <c r="M90" s="7"/>
+      <c r="N90" s="7"/>
+      <c r="O90" s="7"/>
+    </row>
+    <row r="91" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
-      <c r="B91" s="6"/>
-      <c r="C91" s="6"/>
-      <c r="D91" s="6"/>
-      <c r="E91" s="6"/>
-      <c r="F91" s="6"/>
-      <c r="G91" s="6"/>
-      <c r="H91" s="6"/>
-      <c r="I91" s="6"/>
-      <c r="J91" s="6"/>
-      <c r="L91" s="6"/>
-    </row>
-    <row r="92">
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
+      <c r="K91" s="5"/>
+      <c r="L91" s="1"/>
+      <c r="M91" s="7"/>
+      <c r="N91" s="7"/>
+      <c r="O91" s="7"/>
+    </row>
+    <row r="92" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="6"/>
-      <c r="I92" s="6"/>
-      <c r="J92" s="6"/>
-      <c r="L92" s="6"/>
-    </row>
-    <row r="93">
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+      <c r="K92" s="5"/>
+      <c r="L92" s="1"/>
+      <c r="M92" s="7"/>
+      <c r="N92" s="7"/>
+      <c r="O92" s="7"/>
+    </row>
+    <row r="93" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="6"/>
-      <c r="F93" s="6"/>
-      <c r="G93" s="6"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="6"/>
-      <c r="J93" s="6"/>
-      <c r="L93" s="6"/>
-    </row>
-    <row r="94">
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
+      <c r="K93" s="5"/>
+      <c r="L93" s="1"/>
+      <c r="M93" s="7"/>
+      <c r="N93" s="7"/>
+      <c r="O93" s="7"/>
+    </row>
+    <row r="94" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="6"/>
-      <c r="D94" s="6"/>
-      <c r="E94" s="6"/>
-      <c r="F94" s="6"/>
-      <c r="G94" s="6"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
-      <c r="L94" s="6"/>
-    </row>
-    <row r="95">
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
+      <c r="K94" s="5"/>
+      <c r="L94" s="1"/>
+      <c r="M94" s="7"/>
+      <c r="N94" s="7"/>
+      <c r="O94" s="7"/>
+    </row>
+    <row r="95" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="6"/>
-      <c r="D95" s="6"/>
-      <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
-      <c r="G95" s="6"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="6"/>
-      <c r="J95" s="6"/>
-      <c r="L95" s="6"/>
-    </row>
-    <row r="96">
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
+      <c r="K95" s="5"/>
+      <c r="L95" s="1"/>
+      <c r="M95" s="7"/>
+      <c r="N95" s="7"/>
+      <c r="O95" s="7"/>
+    </row>
+    <row r="96" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
-      <c r="B96" s="6"/>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="6"/>
-      <c r="F96" s="6"/>
-      <c r="G96" s="6"/>
-      <c r="H96" s="6"/>
-      <c r="I96" s="6"/>
-      <c r="J96" s="6"/>
-      <c r="L96" s="6"/>
-    </row>
-    <row r="97">
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1"/>
+      <c r="K96" s="5"/>
+      <c r="L96" s="1"/>
+      <c r="M96" s="7"/>
+      <c r="N96" s="7"/>
+      <c r="O96" s="7"/>
+    </row>
+    <row r="97" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="6"/>
-      <c r="D97" s="6"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-      <c r="G97" s="6"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="6"/>
-      <c r="J97" s="6"/>
-      <c r="L97" s="6"/>
-    </row>
-    <row r="98">
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
+      <c r="K97" s="5"/>
+      <c r="L97" s="1"/>
+      <c r="M97" s="7"/>
+      <c r="N97" s="7"/>
+      <c r="O97" s="7"/>
+    </row>
+    <row r="98" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="6"/>
-      <c r="D98" s="6"/>
-      <c r="E98" s="6"/>
-      <c r="F98" s="6"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="6"/>
-      <c r="I98" s="6"/>
-      <c r="J98" s="6"/>
-      <c r="L98" s="6"/>
-    </row>
-    <row r="99">
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+      <c r="J98" s="1"/>
+      <c r="L98" s="1"/>
+      <c r="M98" s="7"/>
+      <c r="N98" s="7"/>
+      <c r="O98" s="7"/>
+    </row>
+    <row r="99" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
-      <c r="G99" s="6"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="6"/>
-      <c r="J99" s="6"/>
-      <c r="L99" s="6"/>
-    </row>
-    <row r="100">
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1"/>
+      <c r="L99" s="1"/>
+      <c r="M99" s="7"/>
+      <c r="N99" s="7"/>
+      <c r="O99" s="7"/>
+    </row>
+    <row r="100" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="6"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
-      <c r="J100" s="6"/>
-      <c r="L100" s="6"/>
-    </row>
-    <row r="101">
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1"/>
+      <c r="L100" s="1"/>
+      <c r="M100" s="7"/>
+      <c r="N100" s="7"/>
+      <c r="O100" s="7"/>
+    </row>
+    <row r="101" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
-      <c r="J101" s="6"/>
-      <c r="L101" s="6"/>
-    </row>
-    <row r="102">
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
+      <c r="L101" s="1"/>
+      <c r="M101" s="7"/>
+      <c r="N101" s="7"/>
+      <c r="O101" s="7"/>
+    </row>
+    <row r="102" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="6"/>
-      <c r="D102" s="6"/>
-      <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
-      <c r="G102" s="6"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6"/>
-      <c r="J102" s="6"/>
-      <c r="L102" s="6"/>
-    </row>
-    <row r="103">
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1"/>
+      <c r="L102" s="1"/>
+      <c r="M102" s="7"/>
+      <c r="N102" s="7"/>
+      <c r="O102" s="7"/>
+    </row>
+    <row r="103" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="D103" s="6"/>
-      <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
-      <c r="G103" s="6"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="6"/>
-      <c r="J103" s="6"/>
-      <c r="L103" s="6"/>
-    </row>
-    <row r="104">
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1"/>
+      <c r="L103" s="1"/>
+      <c r="M103" s="7"/>
+      <c r="N103" s="7"/>
+      <c r="O103" s="7"/>
+    </row>
+    <row r="104" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
-      <c r="B104" s="6"/>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="6"/>
-      <c r="J104" s="6"/>
-      <c r="L104" s="6"/>
-    </row>
-    <row r="105">
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
+      <c r="E104" s="1"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1"/>
+      <c r="L104" s="1"/>
+      <c r="M104" s="7"/>
+      <c r="N104" s="7"/>
+      <c r="O104" s="7"/>
+    </row>
+    <row r="105" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6"/>
-      <c r="G105" s="6"/>
-      <c r="H105" s="6"/>
-      <c r="I105" s="6"/>
-      <c r="J105" s="6"/>
-      <c r="L105" s="6"/>
-    </row>
-    <row r="106">
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
+      <c r="L105" s="1"/>
+      <c r="M105" s="7"/>
+      <c r="N105" s="7"/>
+      <c r="O105" s="7"/>
+    </row>
+    <row r="106" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
-      <c r="B106" s="6"/>
-      <c r="C106" s="6"/>
-      <c r="D106" s="6"/>
-      <c r="E106" s="6"/>
-      <c r="F106" s="6"/>
-      <c r="G106" s="6"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="6"/>
-      <c r="J106" s="6"/>
-      <c r="L106" s="6"/>
-    </row>
-    <row r="107">
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1"/>
+      <c r="L106" s="1"/>
+      <c r="M106" s="7"/>
+      <c r="N106" s="7"/>
+      <c r="O106" s="7"/>
+    </row>
+    <row r="107" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
-      <c r="B107" s="6"/>
-      <c r="C107" s="6"/>
-      <c r="D107" s="6"/>
-      <c r="E107" s="6"/>
-      <c r="F107" s="6"/>
-      <c r="G107" s="6"/>
-      <c r="H107" s="6"/>
-      <c r="I107" s="6"/>
-      <c r="J107" s="6"/>
-      <c r="L107" s="6"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="6"/>
-      <c r="B108" s="6"/>
-      <c r="C108" s="6"/>
-      <c r="D108" s="6"/>
-      <c r="E108" s="6"/>
-      <c r="F108" s="6"/>
-      <c r="G108" s="6"/>
-      <c r="H108" s="6"/>
-      <c r="I108" s="6"/>
-      <c r="J108" s="6"/>
-      <c r="L108" s="6"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="6"/>
-      <c r="D109" s="6"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
-      <c r="G109" s="6"/>
-      <c r="H109" s="6"/>
-      <c r="I109" s="6"/>
-      <c r="J109" s="6"/>
-      <c r="L109" s="6"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="6"/>
-      <c r="B110" s="6"/>
-      <c r="C110" s="6"/>
-      <c r="D110" s="6"/>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-      <c r="G110" s="6"/>
-      <c r="H110" s="6"/>
-      <c r="I110" s="6"/>
-      <c r="J110" s="6"/>
-      <c r="L110" s="6"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="6"/>
-      <c r="B111" s="6"/>
-      <c r="C111" s="6"/>
-      <c r="D111" s="6"/>
-      <c r="E111" s="6"/>
-      <c r="F111" s="6"/>
-      <c r="G111" s="6"/>
-      <c r="H111" s="6"/>
-      <c r="I111" s="6"/>
-      <c r="J111" s="6"/>
-      <c r="L111" s="6"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="6"/>
-      <c r="B112" s="6"/>
-      <c r="C112" s="6"/>
-      <c r="D112" s="6"/>
-      <c r="E112" s="6"/>
-      <c r="F112" s="6"/>
-      <c r="G112" s="6"/>
-      <c r="H112" s="6"/>
-      <c r="I112" s="6"/>
-      <c r="J112" s="6"/>
-      <c r="L112" s="6"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="6"/>
-      <c r="B113" s="6"/>
-      <c r="C113" s="6"/>
-      <c r="D113" s="6"/>
-      <c r="E113" s="6"/>
-      <c r="F113" s="6"/>
-      <c r="G113" s="6"/>
-      <c r="H113" s="6"/>
-      <c r="I113" s="6"/>
-      <c r="J113" s="6"/>
-      <c r="L113" s="6"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="6"/>
-      <c r="B114" s="6"/>
-      <c r="C114" s="6"/>
-      <c r="D114" s="6"/>
-      <c r="E114" s="6"/>
-      <c r="F114" s="6"/>
-      <c r="G114" s="6"/>
-      <c r="H114" s="6"/>
-      <c r="I114" s="6"/>
-      <c r="J114" s="6"/>
-      <c r="L114" s="6"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="6"/>
-      <c r="B115" s="6"/>
-      <c r="C115" s="6"/>
-      <c r="D115" s="6"/>
-      <c r="E115" s="6"/>
-      <c r="F115" s="6"/>
-      <c r="G115" s="6"/>
-      <c r="H115" s="6"/>
-      <c r="I115" s="6"/>
-      <c r="J115" s="6"/>
-      <c r="L115" s="6"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="6"/>
-      <c r="B116" s="6"/>
-      <c r="C116" s="6"/>
-      <c r="D116" s="6"/>
-      <c r="E116" s="6"/>
-      <c r="F116" s="6"/>
-      <c r="G116" s="6"/>
-      <c r="H116" s="6"/>
-      <c r="I116" s="6"/>
-      <c r="J116" s="6"/>
-      <c r="L116" s="6"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
-      <c r="C117" s="6"/>
-      <c r="D117" s="6"/>
-      <c r="E117" s="6"/>
-      <c r="F117" s="6"/>
-      <c r="G117" s="6"/>
-      <c r="H117" s="6"/>
-      <c r="I117" s="6"/>
-      <c r="J117" s="6"/>
-      <c r="L117" s="6"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="6"/>
-      <c r="B118" s="6"/>
-      <c r="C118" s="6"/>
-      <c r="D118" s="6"/>
-      <c r="E118" s="6"/>
-      <c r="F118" s="6"/>
-      <c r="G118" s="6"/>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6"/>
-      <c r="J118" s="6"/>
-      <c r="L118" s="6"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="6"/>
-      <c r="B119" s="6"/>
-      <c r="C119" s="6"/>
-      <c r="D119" s="6"/>
-      <c r="E119" s="6"/>
-      <c r="F119" s="6"/>
-      <c r="G119" s="6"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6"/>
-      <c r="J119" s="6"/>
-      <c r="L119" s="6"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="6"/>
-      <c r="B120" s="6"/>
-      <c r="C120" s="6"/>
-      <c r="D120" s="6"/>
-      <c r="E120" s="6"/>
-      <c r="F120" s="6"/>
-      <c r="G120" s="6"/>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
-      <c r="J120" s="6"/>
-      <c r="L120" s="6"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="6"/>
-      <c r="B121" s="6"/>
-      <c r="C121" s="6"/>
-      <c r="D121" s="6"/>
-      <c r="E121" s="6"/>
-      <c r="F121" s="6"/>
-      <c r="G121" s="6"/>
-      <c r="H121" s="6"/>
-      <c r="I121" s="6"/>
-      <c r="J121" s="6"/>
-      <c r="L121" s="6"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="6"/>
-      <c r="B122" s="6"/>
-      <c r="C122" s="6"/>
-      <c r="D122" s="6"/>
-      <c r="E122" s="6"/>
-      <c r="F122" s="6"/>
-      <c r="G122" s="6"/>
-      <c r="H122" s="6"/>
-      <c r="I122" s="6"/>
-      <c r="J122" s="6"/>
-      <c r="L122" s="6"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="6"/>
-      <c r="B123" s="6"/>
-      <c r="C123" s="6"/>
-      <c r="D123" s="6"/>
-      <c r="E123" s="6"/>
-      <c r="F123" s="6"/>
-      <c r="G123" s="6"/>
-      <c r="H123" s="6"/>
-      <c r="I123" s="6"/>
-      <c r="J123" s="6"/>
-      <c r="L123" s="6"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="6"/>
-      <c r="B124" s="6"/>
-      <c r="C124" s="6"/>
-      <c r="D124" s="6"/>
-      <c r="E124" s="6"/>
-      <c r="F124" s="6"/>
-      <c r="G124" s="6"/>
-      <c r="H124" s="6"/>
-      <c r="I124" s="6"/>
-      <c r="J124" s="6"/>
-      <c r="L124" s="6"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="6"/>
-      <c r="B125" s="6"/>
-      <c r="C125" s="6"/>
-      <c r="D125" s="6"/>
-      <c r="E125" s="6"/>
-      <c r="F125" s="6"/>
-      <c r="G125" s="6"/>
-      <c r="H125" s="6"/>
-      <c r="I125" s="6"/>
-      <c r="J125" s="6"/>
-      <c r="L125" s="6"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="6"/>
-      <c r="B126" s="6"/>
-      <c r="C126" s="6"/>
-      <c r="D126" s="6"/>
-      <c r="E126" s="6"/>
-      <c r="F126" s="6"/>
-      <c r="G126" s="6"/>
-      <c r="H126" s="6"/>
-      <c r="I126" s="6"/>
-      <c r="J126" s="6"/>
-      <c r="L126" s="6"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="6"/>
-      <c r="B127" s="6"/>
-      <c r="C127" s="6"/>
-      <c r="D127" s="6"/>
-      <c r="E127" s="6"/>
-      <c r="F127" s="6"/>
-      <c r="G127" s="6"/>
-      <c r="H127" s="6"/>
-      <c r="I127" s="6"/>
-      <c r="J127" s="6"/>
-      <c r="L127" s="6"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="6"/>
-      <c r="B128" s="6"/>
-      <c r="C128" s="6"/>
-      <c r="D128" s="6"/>
-      <c r="E128" s="6"/>
-      <c r="F128" s="6"/>
-      <c r="G128" s="6"/>
-      <c r="H128" s="6"/>
-      <c r="I128" s="6"/>
-      <c r="J128" s="6"/>
-      <c r="L128" s="6"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="6"/>
-      <c r="B129" s="6"/>
-      <c r="C129" s="6"/>
-      <c r="D129" s="6"/>
-      <c r="E129" s="6"/>
-      <c r="F129" s="6"/>
-      <c r="G129" s="6"/>
-      <c r="H129" s="6"/>
-      <c r="I129" s="6"/>
-      <c r="J129" s="6"/>
-      <c r="L129" s="6"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="6"/>
-      <c r="B130" s="6"/>
-      <c r="C130" s="6"/>
-      <c r="D130" s="6"/>
-      <c r="E130" s="6"/>
-      <c r="F130" s="6"/>
-      <c r="G130" s="6"/>
-      <c r="H130" s="6"/>
-      <c r="I130" s="6"/>
-      <c r="J130" s="6"/>
-      <c r="L130" s="6"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="6"/>
-      <c r="B131" s="6"/>
-      <c r="C131" s="6"/>
-      <c r="D131" s="6"/>
-      <c r="E131" s="6"/>
-      <c r="F131" s="6"/>
-      <c r="G131" s="6"/>
-      <c r="H131" s="6"/>
-      <c r="I131" s="6"/>
-      <c r="J131" s="6"/>
-      <c r="L131" s="6"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="6"/>
-      <c r="B132" s="6"/>
-      <c r="C132" s="6"/>
-      <c r="D132" s="6"/>
-      <c r="E132" s="6"/>
-      <c r="F132" s="6"/>
-      <c r="G132" s="6"/>
-      <c r="H132" s="6"/>
-      <c r="I132" s="6"/>
-      <c r="J132" s="6"/>
-      <c r="L132" s="6"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="6"/>
-      <c r="B133" s="6"/>
-      <c r="C133" s="6"/>
-      <c r="D133" s="6"/>
-      <c r="E133" s="6"/>
-      <c r="F133" s="6"/>
-      <c r="G133" s="6"/>
-      <c r="H133" s="6"/>
-      <c r="I133" s="6"/>
-      <c r="J133" s="6"/>
-      <c r="L133" s="6"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="6"/>
-      <c r="B134" s="6"/>
-      <c r="C134" s="6"/>
-      <c r="D134" s="6"/>
-      <c r="E134" s="6"/>
-      <c r="F134" s="6"/>
-      <c r="G134" s="6"/>
-      <c r="H134" s="6"/>
-      <c r="I134" s="6"/>
-      <c r="J134" s="6"/>
-      <c r="L134" s="6"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="6"/>
-      <c r="B135" s="6"/>
-      <c r="C135" s="6"/>
-      <c r="D135" s="6"/>
-      <c r="E135" s="6"/>
-      <c r="F135" s="6"/>
-      <c r="G135" s="6"/>
-      <c r="H135" s="6"/>
-      <c r="I135" s="6"/>
-      <c r="J135" s="6"/>
-      <c r="L135" s="6"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="6"/>
-      <c r="B136" s="6"/>
-      <c r="C136" s="6"/>
-      <c r="D136" s="6"/>
-      <c r="E136" s="6"/>
-      <c r="F136" s="6"/>
-      <c r="G136" s="6"/>
-      <c r="H136" s="6"/>
-      <c r="I136" s="6"/>
-      <c r="J136" s="6"/>
-      <c r="L136" s="6"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="6"/>
-      <c r="B137" s="6"/>
-      <c r="C137" s="6"/>
-      <c r="D137" s="6"/>
-      <c r="E137" s="6"/>
-      <c r="F137" s="6"/>
-      <c r="G137" s="6"/>
-      <c r="H137" s="6"/>
-      <c r="I137" s="6"/>
-      <c r="J137" s="6"/>
-      <c r="L137" s="6"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="6"/>
-      <c r="B138" s="6"/>
-      <c r="C138" s="6"/>
-      <c r="D138" s="6"/>
-      <c r="E138" s="6"/>
-      <c r="F138" s="6"/>
-      <c r="G138" s="6"/>
-      <c r="H138" s="6"/>
-      <c r="I138" s="6"/>
-      <c r="J138" s="6"/>
-      <c r="L138" s="6"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="6"/>
-      <c r="B139" s="6"/>
-      <c r="C139" s="6"/>
-      <c r="D139" s="6"/>
-      <c r="E139" s="6"/>
-      <c r="F139" s="6"/>
-      <c r="G139" s="6"/>
-      <c r="H139" s="6"/>
-      <c r="I139" s="6"/>
-      <c r="J139" s="6"/>
-      <c r="L139" s="6"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="6"/>
-      <c r="B140" s="6"/>
-      <c r="C140" s="6"/>
-      <c r="D140" s="6"/>
-      <c r="E140" s="6"/>
-      <c r="F140" s="6"/>
-      <c r="G140" s="6"/>
-      <c r="H140" s="6"/>
-      <c r="I140" s="6"/>
-      <c r="J140" s="6"/>
-      <c r="L140" s="6"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="6"/>
-      <c r="B141" s="6"/>
-      <c r="C141" s="6"/>
-      <c r="D141" s="6"/>
-      <c r="E141" s="6"/>
-      <c r="F141" s="6"/>
-      <c r="G141" s="6"/>
-      <c r="H141" s="6"/>
-      <c r="I141" s="6"/>
-      <c r="J141" s="6"/>
-      <c r="L141" s="6"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="6"/>
-      <c r="B142" s="6"/>
-      <c r="C142" s="6"/>
-      <c r="D142" s="6"/>
-      <c r="E142" s="6"/>
-      <c r="F142" s="6"/>
-      <c r="G142" s="6"/>
-      <c r="H142" s="6"/>
-      <c r="I142" s="6"/>
-      <c r="J142" s="6"/>
-      <c r="L142" s="6"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="6"/>
-      <c r="B143" s="6"/>
-      <c r="C143" s="6"/>
-      <c r="D143" s="6"/>
-      <c r="E143" s="6"/>
-      <c r="F143" s="6"/>
-      <c r="G143" s="6"/>
-      <c r="H143" s="6"/>
-      <c r="I143" s="6"/>
-      <c r="J143" s="6"/>
-      <c r="L143" s="6"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="6"/>
-      <c r="B144" s="6"/>
-      <c r="C144" s="6"/>
-      <c r="D144" s="6"/>
-      <c r="E144" s="6"/>
-      <c r="F144" s="6"/>
-      <c r="G144" s="6"/>
-      <c r="H144" s="6"/>
-      <c r="I144" s="6"/>
-      <c r="J144" s="6"/>
-      <c r="L144" s="6"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="6"/>
-      <c r="B145" s="6"/>
-      <c r="C145" s="6"/>
-      <c r="D145" s="6"/>
-      <c r="E145" s="6"/>
-      <c r="F145" s="6"/>
-      <c r="G145" s="6"/>
-      <c r="H145" s="6"/>
-      <c r="I145" s="6"/>
-      <c r="J145" s="6"/>
-      <c r="L145" s="6"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="6"/>
-      <c r="B146" s="6"/>
-      <c r="C146" s="6"/>
-      <c r="D146" s="6"/>
-      <c r="E146" s="6"/>
-      <c r="F146" s="6"/>
-      <c r="G146" s="6"/>
-      <c r="H146" s="6"/>
-      <c r="I146" s="6"/>
-      <c r="J146" s="6"/>
-      <c r="L146" s="6"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="6"/>
-      <c r="B147" s="6"/>
-      <c r="C147" s="6"/>
-      <c r="D147" s="6"/>
-      <c r="E147" s="6"/>
-      <c r="F147" s="6"/>
-      <c r="G147" s="6"/>
-      <c r="H147" s="6"/>
-      <c r="I147" s="6"/>
-      <c r="J147" s="6"/>
-      <c r="L147" s="6"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="6"/>
-      <c r="B148" s="6"/>
-      <c r="C148" s="6"/>
-      <c r="D148" s="6"/>
-      <c r="E148" s="6"/>
-      <c r="F148" s="6"/>
-      <c r="G148" s="6"/>
-      <c r="H148" s="6"/>
-      <c r="I148" s="6"/>
-      <c r="J148" s="6"/>
-      <c r="L148" s="6"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="6"/>
-      <c r="B149" s="6"/>
-      <c r="C149" s="6"/>
-      <c r="D149" s="6"/>
-      <c r="E149" s="6"/>
-      <c r="F149" s="6"/>
-      <c r="G149" s="6"/>
-      <c r="H149" s="6"/>
-      <c r="I149" s="6"/>
-      <c r="J149" s="6"/>
-      <c r="L149" s="6"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="6"/>
-      <c r="B150" s="6"/>
-      <c r="C150" s="6"/>
-      <c r="D150" s="6"/>
-      <c r="E150" s="6"/>
-      <c r="F150" s="6"/>
-      <c r="G150" s="6"/>
-      <c r="H150" s="6"/>
-      <c r="I150" s="6"/>
-      <c r="J150" s="6"/>
-      <c r="L150" s="6"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="6"/>
-      <c r="B151" s="6"/>
-      <c r="C151" s="6"/>
-      <c r="D151" s="6"/>
-      <c r="E151" s="6"/>
-      <c r="F151" s="6"/>
-      <c r="G151" s="6"/>
-      <c r="H151" s="6"/>
-      <c r="I151" s="6"/>
-      <c r="J151" s="6"/>
-      <c r="L151" s="6"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="6"/>
-      <c r="B152" s="6"/>
-      <c r="C152" s="6"/>
-      <c r="D152" s="6"/>
-      <c r="E152" s="6"/>
-      <c r="F152" s="6"/>
-      <c r="G152" s="6"/>
-      <c r="H152" s="6"/>
-      <c r="I152" s="6"/>
-      <c r="J152" s="6"/>
-      <c r="L152" s="6"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="6"/>
-      <c r="B153" s="6"/>
-      <c r="C153" s="6"/>
-      <c r="D153" s="6"/>
-      <c r="E153" s="6"/>
-      <c r="F153" s="6"/>
-      <c r="G153" s="6"/>
-      <c r="H153" s="6"/>
-      <c r="I153" s="6"/>
-      <c r="J153" s="6"/>
-      <c r="L153" s="6"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="6"/>
-      <c r="B154" s="6"/>
-      <c r="C154" s="6"/>
-      <c r="D154" s="6"/>
-      <c r="E154" s="6"/>
-      <c r="F154" s="6"/>
-      <c r="G154" s="6"/>
-      <c r="H154" s="6"/>
-      <c r="I154" s="6"/>
-      <c r="J154" s="6"/>
-      <c r="L154" s="6"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="6"/>
-      <c r="B155" s="6"/>
-      <c r="C155" s="6"/>
-      <c r="D155" s="6"/>
-      <c r="E155" s="6"/>
-      <c r="F155" s="6"/>
-      <c r="G155" s="6"/>
-      <c r="H155" s="6"/>
-      <c r="I155" s="6"/>
-      <c r="J155" s="6"/>
-      <c r="L155" s="6"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="6"/>
-      <c r="B156" s="6"/>
-      <c r="C156" s="6"/>
-      <c r="D156" s="6"/>
-      <c r="E156" s="6"/>
-      <c r="F156" s="6"/>
-      <c r="G156" s="6"/>
-      <c r="H156" s="6"/>
-      <c r="I156" s="6"/>
-      <c r="J156" s="6"/>
-      <c r="L156" s="6"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="6"/>
-      <c r="B157" s="6"/>
-      <c r="C157" s="6"/>
-      <c r="D157" s="6"/>
-      <c r="E157" s="6"/>
-      <c r="F157" s="6"/>
-      <c r="G157" s="6"/>
-      <c r="H157" s="6"/>
-      <c r="I157" s="6"/>
-      <c r="J157" s="6"/>
-      <c r="L157" s="6"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="6"/>
-      <c r="B158" s="6"/>
-      <c r="C158" s="6"/>
-      <c r="D158" s="6"/>
-      <c r="E158" s="6"/>
-      <c r="F158" s="6"/>
-      <c r="G158" s="6"/>
-      <c r="H158" s="6"/>
-      <c r="I158" s="6"/>
-      <c r="J158" s="6"/>
-      <c r="L158" s="6"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="6"/>
-      <c r="B159" s="6"/>
-      <c r="C159" s="6"/>
-      <c r="D159" s="6"/>
-      <c r="E159" s="6"/>
-      <c r="F159" s="6"/>
-      <c r="G159" s="6"/>
-      <c r="H159" s="6"/>
-      <c r="I159" s="6"/>
-      <c r="J159" s="6"/>
-      <c r="L159" s="6"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="6"/>
-      <c r="B160" s="6"/>
-      <c r="C160" s="6"/>
-      <c r="D160" s="6"/>
-      <c r="E160" s="6"/>
-      <c r="F160" s="6"/>
-      <c r="G160" s="6"/>
-      <c r="H160" s="6"/>
-      <c r="I160" s="6"/>
-      <c r="J160" s="6"/>
-      <c r="L160" s="6"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="6"/>
-      <c r="B161" s="6"/>
-      <c r="C161" s="6"/>
-      <c r="D161" s="6"/>
-      <c r="E161" s="6"/>
-      <c r="F161" s="6"/>
-      <c r="G161" s="6"/>
-      <c r="H161" s="6"/>
-      <c r="I161" s="6"/>
-      <c r="J161" s="6"/>
-      <c r="L161" s="6"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="6"/>
-      <c r="B162" s="6"/>
-      <c r="C162" s="6"/>
-      <c r="D162" s="6"/>
-      <c r="E162" s="6"/>
-      <c r="F162" s="6"/>
-      <c r="G162" s="6"/>
-      <c r="H162" s="6"/>
-      <c r="I162" s="6"/>
-      <c r="J162" s="6"/>
-      <c r="L162" s="6"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="6"/>
-      <c r="B163" s="6"/>
-      <c r="C163" s="6"/>
-      <c r="D163" s="6"/>
-      <c r="E163" s="6"/>
-      <c r="F163" s="6"/>
-      <c r="G163" s="6"/>
-      <c r="H163" s="6"/>
-      <c r="I163" s="6"/>
-      <c r="J163" s="6"/>
-      <c r="L163" s="6"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="6"/>
-      <c r="B164" s="6"/>
-      <c r="C164" s="6"/>
-      <c r="D164" s="6"/>
-      <c r="E164" s="6"/>
-      <c r="F164" s="6"/>
-      <c r="G164" s="6"/>
-      <c r="H164" s="6"/>
-      <c r="I164" s="6"/>
-      <c r="J164" s="6"/>
-      <c r="L164" s="6"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="6"/>
-      <c r="B165" s="6"/>
-      <c r="C165" s="6"/>
-      <c r="D165" s="6"/>
-      <c r="E165" s="6"/>
-      <c r="F165" s="6"/>
-      <c r="G165" s="6"/>
-      <c r="H165" s="6"/>
-      <c r="I165" s="6"/>
-      <c r="J165" s="6"/>
-      <c r="L165" s="6"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="6"/>
-      <c r="B166" s="6"/>
-      <c r="C166" s="6"/>
-      <c r="D166" s="6"/>
-      <c r="E166" s="6"/>
-      <c r="F166" s="6"/>
-      <c r="G166" s="6"/>
-      <c r="H166" s="6"/>
-      <c r="I166" s="6"/>
-      <c r="J166" s="6"/>
-      <c r="L166" s="6"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="6"/>
-      <c r="B167" s="6"/>
-      <c r="C167" s="6"/>
-      <c r="D167" s="6"/>
-      <c r="E167" s="6"/>
-      <c r="F167" s="6"/>
-      <c r="G167" s="6"/>
-      <c r="H167" s="6"/>
-      <c r="I167" s="6"/>
-      <c r="J167" s="6"/>
-      <c r="L167" s="6"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="6"/>
-      <c r="B168" s="6"/>
-      <c r="C168" s="6"/>
-      <c r="D168" s="6"/>
-      <c r="E168" s="6"/>
-      <c r="F168" s="6"/>
-      <c r="G168" s="6"/>
-      <c r="H168" s="6"/>
-      <c r="I168" s="6"/>
-      <c r="J168" s="6"/>
-      <c r="L168" s="6"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="6"/>
-      <c r="B169" s="6"/>
-      <c r="C169" s="6"/>
-      <c r="D169" s="6"/>
-      <c r="E169" s="6"/>
-      <c r="F169" s="6"/>
-      <c r="G169" s="6"/>
-      <c r="H169" s="6"/>
-      <c r="I169" s="6"/>
-      <c r="J169" s="6"/>
-      <c r="L169" s="6"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="6"/>
-      <c r="B170" s="6"/>
-      <c r="C170" s="6"/>
-      <c r="D170" s="6"/>
-      <c r="E170" s="6"/>
-      <c r="F170" s="6"/>
-      <c r="G170" s="6"/>
-      <c r="H170" s="6"/>
-      <c r="I170" s="6"/>
-      <c r="J170" s="6"/>
-      <c r="L170" s="6"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="6"/>
-      <c r="B171" s="6"/>
-      <c r="C171" s="6"/>
-      <c r="D171" s="6"/>
-      <c r="E171" s="6"/>
-      <c r="F171" s="6"/>
-      <c r="G171" s="6"/>
-      <c r="H171" s="6"/>
-      <c r="I171" s="6"/>
-      <c r="J171" s="6"/>
-      <c r="L171" s="6"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="6"/>
-      <c r="B172" s="6"/>
-      <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
-      <c r="E172" s="6"/>
-      <c r="F172" s="6"/>
-      <c r="G172" s="6"/>
-      <c r="H172" s="6"/>
-      <c r="I172" s="6"/>
-      <c r="J172" s="6"/>
-      <c r="L172" s="6"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="6"/>
-      <c r="B173" s="6"/>
-      <c r="C173" s="6"/>
-      <c r="D173" s="6"/>
-      <c r="E173" s="6"/>
-      <c r="F173" s="6"/>
-      <c r="G173" s="6"/>
-      <c r="H173" s="6"/>
-      <c r="I173" s="6"/>
-      <c r="J173" s="6"/>
-      <c r="L173" s="6"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="6"/>
-      <c r="B174" s="6"/>
-      <c r="C174" s="6"/>
-      <c r="D174" s="6"/>
-      <c r="E174" s="6"/>
-      <c r="F174" s="6"/>
-      <c r="G174" s="6"/>
-      <c r="H174" s="6"/>
-      <c r="I174" s="6"/>
-      <c r="J174" s="6"/>
-      <c r="L174" s="6"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="6"/>
-      <c r="B175" s="6"/>
-      <c r="C175" s="6"/>
-      <c r="D175" s="6"/>
-      <c r="E175" s="6"/>
-      <c r="F175" s="6"/>
-      <c r="G175" s="6"/>
-      <c r="H175" s="6"/>
-      <c r="I175" s="6"/>
-      <c r="J175" s="6"/>
-      <c r="L175" s="6"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="6"/>
-      <c r="B176" s="6"/>
-      <c r="C176" s="6"/>
-      <c r="D176" s="6"/>
-      <c r="E176" s="6"/>
-      <c r="F176" s="6"/>
-      <c r="G176" s="6"/>
-      <c r="H176" s="6"/>
-      <c r="I176" s="6"/>
-      <c r="J176" s="6"/>
-      <c r="L176" s="6"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="6"/>
-      <c r="B177" s="6"/>
-      <c r="C177" s="6"/>
-      <c r="D177" s="6"/>
-      <c r="E177" s="6"/>
-      <c r="F177" s="6"/>
-      <c r="G177" s="6"/>
-      <c r="H177" s="6"/>
-      <c r="I177" s="6"/>
-      <c r="J177" s="6"/>
-      <c r="L177" s="6"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="6"/>
-      <c r="B178" s="6"/>
-      <c r="C178" s="6"/>
-      <c r="D178" s="6"/>
-      <c r="E178" s="6"/>
-      <c r="F178" s="6"/>
-      <c r="G178" s="6"/>
-      <c r="H178" s="6"/>
-      <c r="I178" s="6"/>
-      <c r="J178" s="6"/>
-      <c r="L178" s="6"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="6"/>
-      <c r="B179" s="6"/>
-      <c r="C179" s="6"/>
-      <c r="D179" s="6"/>
-      <c r="E179" s="6"/>
-      <c r="F179" s="6"/>
-      <c r="G179" s="6"/>
-      <c r="H179" s="6"/>
-      <c r="I179" s="6"/>
-      <c r="J179" s="6"/>
-      <c r="L179" s="6"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="6"/>
-      <c r="B180" s="6"/>
-      <c r="C180" s="6"/>
-      <c r="D180" s="6"/>
-      <c r="E180" s="6"/>
-      <c r="F180" s="6"/>
-      <c r="G180" s="6"/>
-      <c r="H180" s="6"/>
-      <c r="I180" s="6"/>
-      <c r="J180" s="6"/>
-      <c r="L180" s="6"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="6"/>
-      <c r="B181" s="6"/>
-      <c r="C181" s="6"/>
-      <c r="D181" s="6"/>
-      <c r="E181" s="6"/>
-      <c r="F181" s="6"/>
-      <c r="G181" s="6"/>
-      <c r="H181" s="6"/>
-      <c r="I181" s="6"/>
-      <c r="J181" s="6"/>
-      <c r="L181" s="6"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="6"/>
-      <c r="B182" s="6"/>
-      <c r="C182" s="6"/>
-      <c r="D182" s="6"/>
-      <c r="E182" s="6"/>
-      <c r="F182" s="6"/>
-      <c r="G182" s="6"/>
-      <c r="H182" s="6"/>
-      <c r="I182" s="6"/>
-      <c r="J182" s="6"/>
-      <c r="L182" s="6"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="6"/>
-      <c r="B183" s="6"/>
-      <c r="C183" s="6"/>
-      <c r="D183" s="6"/>
-      <c r="E183" s="6"/>
-      <c r="F183" s="6"/>
-      <c r="G183" s="6"/>
-      <c r="H183" s="6"/>
-      <c r="I183" s="6"/>
-      <c r="J183" s="6"/>
-      <c r="L183" s="6"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="6"/>
-      <c r="B184" s="6"/>
-      <c r="C184" s="6"/>
-      <c r="D184" s="6"/>
-      <c r="E184" s="6"/>
-      <c r="F184" s="6"/>
-      <c r="G184" s="6"/>
-      <c r="H184" s="6"/>
-      <c r="I184" s="6"/>
-      <c r="J184" s="6"/>
-      <c r="L184" s="6"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="6"/>
-      <c r="B185" s="6"/>
-      <c r="C185" s="6"/>
-      <c r="D185" s="6"/>
-      <c r="E185" s="6"/>
-      <c r="F185" s="6"/>
-      <c r="G185" s="6"/>
-      <c r="H185" s="6"/>
-      <c r="I185" s="6"/>
-      <c r="J185" s="6"/>
-      <c r="L185" s="6"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="6"/>
-      <c r="B186" s="6"/>
-      <c r="C186" s="6"/>
-      <c r="D186" s="6"/>
-      <c r="E186" s="6"/>
-      <c r="F186" s="6"/>
-      <c r="G186" s="6"/>
-      <c r="H186" s="6"/>
-      <c r="I186" s="6"/>
-      <c r="J186" s="6"/>
-      <c r="L186" s="6"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="6"/>
-      <c r="B187" s="6"/>
-      <c r="C187" s="6"/>
-      <c r="D187" s="6"/>
-      <c r="E187" s="6"/>
-      <c r="F187" s="6"/>
-      <c r="G187" s="6"/>
-      <c r="H187" s="6"/>
-      <c r="I187" s="6"/>
-      <c r="J187" s="6"/>
-      <c r="L187" s="6"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="6"/>
-      <c r="B188" s="6"/>
-      <c r="C188" s="6"/>
-      <c r="D188" s="6"/>
-      <c r="E188" s="6"/>
-      <c r="F188" s="6"/>
-      <c r="G188" s="6"/>
-      <c r="H188" s="6"/>
-      <c r="I188" s="6"/>
-      <c r="J188" s="6"/>
-      <c r="L188" s="6"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="6"/>
-      <c r="B189" s="6"/>
-      <c r="C189" s="6"/>
-      <c r="D189" s="6"/>
-      <c r="E189" s="6"/>
-      <c r="F189" s="6"/>
-      <c r="G189" s="6"/>
-      <c r="H189" s="6"/>
-      <c r="I189" s="6"/>
-      <c r="J189" s="6"/>
-      <c r="L189" s="6"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="6"/>
-      <c r="B190" s="6"/>
-      <c r="C190" s="6"/>
-      <c r="D190" s="6"/>
-      <c r="E190" s="6"/>
-      <c r="F190" s="6"/>
-      <c r="G190" s="6"/>
-      <c r="H190" s="6"/>
-      <c r="I190" s="6"/>
-      <c r="J190" s="6"/>
-      <c r="L190" s="6"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="6"/>
-      <c r="B191" s="6"/>
-      <c r="C191" s="6"/>
-      <c r="D191" s="6"/>
-      <c r="E191" s="6"/>
-      <c r="F191" s="6"/>
-      <c r="G191" s="6"/>
-      <c r="H191" s="6"/>
-      <c r="I191" s="6"/>
-      <c r="J191" s="6"/>
-      <c r="L191" s="6"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="6"/>
-      <c r="B192" s="6"/>
-      <c r="C192" s="6"/>
-      <c r="D192" s="6"/>
-      <c r="E192" s="6"/>
-      <c r="F192" s="6"/>
-      <c r="G192" s="6"/>
-      <c r="H192" s="6"/>
-      <c r="I192" s="6"/>
-      <c r="J192" s="6"/>
-      <c r="L192" s="6"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="6"/>
-      <c r="B193" s="6"/>
-      <c r="C193" s="6"/>
-      <c r="D193" s="6"/>
-      <c r="E193" s="6"/>
-      <c r="F193" s="6"/>
-      <c r="G193" s="6"/>
-      <c r="H193" s="6"/>
-      <c r="I193" s="6"/>
-      <c r="J193" s="6"/>
-      <c r="L193" s="6"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="6"/>
-      <c r="B194" s="6"/>
-      <c r="C194" s="6"/>
-      <c r="D194" s="6"/>
-      <c r="E194" s="6"/>
-      <c r="F194" s="6"/>
-      <c r="G194" s="6"/>
-      <c r="H194" s="6"/>
-      <c r="I194" s="6"/>
-      <c r="J194" s="6"/>
-      <c r="L194" s="6"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="6"/>
-      <c r="B195" s="6"/>
-      <c r="C195" s="6"/>
-      <c r="D195" s="6"/>
-      <c r="E195" s="6"/>
-      <c r="F195" s="6"/>
-      <c r="G195" s="6"/>
-      <c r="H195" s="6"/>
-      <c r="I195" s="6"/>
-      <c r="J195" s="6"/>
-      <c r="L195" s="6"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="6"/>
-      <c r="B196" s="6"/>
-      <c r="C196" s="6"/>
-      <c r="D196" s="6"/>
-      <c r="E196" s="6"/>
-      <c r="F196" s="6"/>
-      <c r="G196" s="6"/>
-      <c r="H196" s="6"/>
-      <c r="I196" s="6"/>
-      <c r="J196" s="6"/>
-      <c r="L196" s="6"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="6"/>
-      <c r="B197" s="6"/>
-      <c r="C197" s="6"/>
-      <c r="D197" s="6"/>
-      <c r="E197" s="6"/>
-      <c r="F197" s="6"/>
-      <c r="G197" s="6"/>
-      <c r="H197" s="6"/>
-      <c r="I197" s="6"/>
-      <c r="J197" s="6"/>
-      <c r="L197" s="6"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="6"/>
-      <c r="B198" s="6"/>
-      <c r="C198" s="6"/>
-      <c r="D198" s="6"/>
-      <c r="E198" s="6"/>
-      <c r="F198" s="6"/>
-      <c r="G198" s="6"/>
-      <c r="H198" s="6"/>
-      <c r="I198" s="6"/>
-      <c r="J198" s="6"/>
-      <c r="L198" s="6"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="6"/>
-      <c r="B199" s="6"/>
-      <c r="C199" s="6"/>
-      <c r="D199" s="6"/>
-      <c r="E199" s="6"/>
-      <c r="F199" s="6"/>
-      <c r="G199" s="6"/>
-      <c r="H199" s="6"/>
-      <c r="I199" s="6"/>
-      <c r="J199" s="6"/>
-      <c r="L199" s="6"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="6"/>
-      <c r="B200" s="6"/>
-      <c r="C200" s="6"/>
-      <c r="D200" s="6"/>
-      <c r="E200" s="6"/>
-      <c r="F200" s="6"/>
-      <c r="G200" s="6"/>
-      <c r="H200" s="6"/>
-      <c r="I200" s="6"/>
-      <c r="J200" s="6"/>
-      <c r="L200" s="6"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="6"/>
-      <c r="B201" s="6"/>
-      <c r="C201" s="6"/>
-      <c r="D201" s="6"/>
-      <c r="E201" s="6"/>
-      <c r="F201" s="6"/>
-      <c r="G201" s="6"/>
-      <c r="H201" s="6"/>
-      <c r="I201" s="6"/>
-      <c r="J201" s="6"/>
-      <c r="L201" s="6"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="6"/>
-      <c r="B202" s="6"/>
-      <c r="C202" s="6"/>
-      <c r="D202" s="6"/>
-      <c r="E202" s="6"/>
-      <c r="F202" s="6"/>
-      <c r="G202" s="6"/>
-      <c r="H202" s="6"/>
-      <c r="I202" s="6"/>
-      <c r="J202" s="6"/>
-      <c r="L202" s="6"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="6"/>
-      <c r="B203" s="6"/>
-      <c r="C203" s="6"/>
-      <c r="D203" s="6"/>
-      <c r="E203" s="6"/>
-      <c r="F203" s="6"/>
-      <c r="G203" s="6"/>
-      <c r="H203" s="6"/>
-      <c r="I203" s="6"/>
-      <c r="J203" s="6"/>
-      <c r="L203" s="6"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="6"/>
-      <c r="B204" s="6"/>
-      <c r="C204" s="6"/>
-      <c r="D204" s="6"/>
-      <c r="E204" s="6"/>
-      <c r="F204" s="6"/>
-      <c r="G204" s="6"/>
-      <c r="H204" s="6"/>
-      <c r="I204" s="6"/>
-      <c r="J204" s="6"/>
-      <c r="L204" s="6"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="6"/>
-      <c r="B205" s="6"/>
-      <c r="C205" s="6"/>
-      <c r="D205" s="6"/>
-      <c r="E205" s="6"/>
-      <c r="F205" s="6"/>
-      <c r="G205" s="6"/>
-      <c r="H205" s="6"/>
-      <c r="I205" s="6"/>
-      <c r="J205" s="6"/>
-      <c r="L205" s="6"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="6"/>
-      <c r="B206" s="6"/>
-      <c r="C206" s="6"/>
-      <c r="D206" s="6"/>
-      <c r="E206" s="6"/>
-      <c r="F206" s="6"/>
-      <c r="G206" s="6"/>
-      <c r="H206" s="6"/>
-      <c r="I206" s="6"/>
-      <c r="J206" s="6"/>
-      <c r="L206" s="6"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="6"/>
-      <c r="B207" s="6"/>
-      <c r="C207" s="6"/>
-      <c r="D207" s="6"/>
-      <c r="E207" s="6"/>
-      <c r="F207" s="6"/>
-      <c r="G207" s="6"/>
-      <c r="H207" s="6"/>
-      <c r="I207" s="6"/>
-      <c r="J207" s="6"/>
-      <c r="L207" s="6"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="6"/>
-      <c r="B208" s="6"/>
-      <c r="C208" s="6"/>
-      <c r="D208" s="6"/>
-      <c r="E208" s="6"/>
-      <c r="F208" s="6"/>
-      <c r="G208" s="6"/>
-      <c r="H208" s="6"/>
-      <c r="I208" s="6"/>
-      <c r="J208" s="6"/>
-      <c r="L208" s="6"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="6"/>
-      <c r="B209" s="6"/>
-      <c r="C209" s="6"/>
-      <c r="D209" s="6"/>
-      <c r="E209" s="6"/>
-      <c r="F209" s="6"/>
-      <c r="G209" s="6"/>
-      <c r="H209" s="6"/>
-      <c r="I209" s="6"/>
-      <c r="J209" s="6"/>
-      <c r="L209" s="6"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="6"/>
-      <c r="B210" s="6"/>
-      <c r="C210" s="6"/>
-      <c r="D210" s="6"/>
-      <c r="E210" s="6"/>
-      <c r="F210" s="6"/>
-      <c r="G210" s="6"/>
-      <c r="H210" s="6"/>
-      <c r="I210" s="6"/>
-      <c r="J210" s="6"/>
-      <c r="L210" s="6"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="6"/>
-      <c r="B211" s="6"/>
-      <c r="C211" s="6"/>
-      <c r="D211" s="6"/>
-      <c r="E211" s="6"/>
-      <c r="F211" s="6"/>
-      <c r="G211" s="6"/>
-      <c r="H211" s="6"/>
-      <c r="I211" s="6"/>
-      <c r="J211" s="6"/>
-      <c r="L211" s="6"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="6"/>
-      <c r="B212" s="6"/>
-      <c r="C212" s="6"/>
-      <c r="D212" s="6"/>
-      <c r="E212" s="6"/>
-      <c r="F212" s="6"/>
-      <c r="G212" s="6"/>
-      <c r="H212" s="6"/>
-      <c r="I212" s="6"/>
-      <c r="J212" s="6"/>
-      <c r="L212" s="6"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="6"/>
-      <c r="B213" s="6"/>
-      <c r="C213" s="6"/>
-      <c r="D213" s="6"/>
-      <c r="E213" s="6"/>
-      <c r="F213" s="6"/>
-      <c r="G213" s="6"/>
-      <c r="H213" s="6"/>
-      <c r="I213" s="6"/>
-      <c r="J213" s="6"/>
-      <c r="L213" s="6"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="6"/>
-      <c r="B214" s="6"/>
-      <c r="C214" s="6"/>
-      <c r="D214" s="6"/>
-      <c r="E214" s="6"/>
-      <c r="F214" s="6"/>
-      <c r="G214" s="6"/>
-      <c r="H214" s="6"/>
-      <c r="I214" s="6"/>
-      <c r="J214" s="6"/>
-      <c r="L214" s="6"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="6"/>
-      <c r="B215" s="6"/>
-      <c r="C215" s="6"/>
-      <c r="D215" s="6"/>
-      <c r="E215" s="6"/>
-      <c r="F215" s="6"/>
-      <c r="G215" s="6"/>
-      <c r="H215" s="6"/>
-      <c r="I215" s="6"/>
-      <c r="J215" s="6"/>
-      <c r="L215" s="6"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="6"/>
-      <c r="B216" s="6"/>
-      <c r="C216" s="6"/>
-      <c r="D216" s="6"/>
-      <c r="E216" s="6"/>
-      <c r="F216" s="6"/>
-      <c r="G216" s="6"/>
-      <c r="H216" s="6"/>
-      <c r="I216" s="6"/>
-      <c r="J216" s="6"/>
-      <c r="L216" s="6"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="6"/>
-      <c r="B217" s="6"/>
-      <c r="C217" s="6"/>
-      <c r="D217" s="6"/>
-      <c r="E217" s="6"/>
-      <c r="F217" s="6"/>
-      <c r="G217" s="6"/>
-      <c r="H217" s="6"/>
-      <c r="I217" s="6"/>
-      <c r="J217" s="6"/>
-      <c r="L217" s="6"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="6"/>
-      <c r="B218" s="6"/>
-      <c r="C218" s="6"/>
-      <c r="D218" s="6"/>
-      <c r="E218" s="6"/>
-      <c r="F218" s="6"/>
-      <c r="G218" s="6"/>
-      <c r="H218" s="6"/>
-      <c r="I218" s="6"/>
-      <c r="J218" s="6"/>
-      <c r="L218" s="6"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="6"/>
-      <c r="B219" s="6"/>
-      <c r="C219" s="6"/>
-      <c r="D219" s="6"/>
-      <c r="E219" s="6"/>
-      <c r="F219" s="6"/>
-      <c r="G219" s="6"/>
-      <c r="H219" s="6"/>
-      <c r="I219" s="6"/>
-      <c r="J219" s="6"/>
-      <c r="L219" s="6"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="6"/>
-      <c r="B220" s="6"/>
-      <c r="C220" s="6"/>
-      <c r="D220" s="6"/>
-      <c r="E220" s="6"/>
-      <c r="F220" s="6"/>
-      <c r="G220" s="6"/>
-      <c r="H220" s="6"/>
-      <c r="I220" s="6"/>
-      <c r="J220" s="6"/>
-      <c r="L220" s="6"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="6"/>
-      <c r="B221" s="6"/>
-      <c r="C221" s="6"/>
-      <c r="D221" s="6"/>
-      <c r="E221" s="6"/>
-      <c r="F221" s="6"/>
-      <c r="G221" s="6"/>
-      <c r="H221" s="6"/>
-      <c r="I221" s="6"/>
-      <c r="J221" s="6"/>
-      <c r="L221" s="6"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="6"/>
-      <c r="B222" s="6"/>
-      <c r="C222" s="6"/>
-      <c r="D222" s="6"/>
-      <c r="E222" s="6"/>
-      <c r="F222" s="6"/>
-      <c r="G222" s="6"/>
-      <c r="H222" s="6"/>
-      <c r="I222" s="6"/>
-      <c r="J222" s="6"/>
-      <c r="L222" s="6"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="6"/>
-      <c r="B223" s="6"/>
-      <c r="C223" s="6"/>
-      <c r="D223" s="6"/>
-      <c r="E223" s="6"/>
-      <c r="F223" s="6"/>
-      <c r="G223" s="6"/>
-      <c r="H223" s="6"/>
-      <c r="I223" s="6"/>
-      <c r="J223" s="6"/>
-      <c r="L223" s="6"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="6"/>
-      <c r="B224" s="6"/>
-      <c r="C224" s="6"/>
-      <c r="D224" s="6"/>
-      <c r="E224" s="6"/>
-      <c r="F224" s="6"/>
-      <c r="G224" s="6"/>
-      <c r="H224" s="6"/>
-      <c r="I224" s="6"/>
-      <c r="J224" s="6"/>
-      <c r="L224" s="6"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="6"/>
-      <c r="B225" s="6"/>
-      <c r="C225" s="6"/>
-      <c r="D225" s="6"/>
-      <c r="E225" s="6"/>
-      <c r="F225" s="6"/>
-      <c r="G225" s="6"/>
-      <c r="H225" s="6"/>
-      <c r="I225" s="6"/>
-      <c r="J225" s="6"/>
-      <c r="L225" s="6"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="6"/>
-      <c r="B226" s="6"/>
-      <c r="C226" s="6"/>
-      <c r="D226" s="6"/>
-      <c r="E226" s="6"/>
-      <c r="F226" s="6"/>
-      <c r="G226" s="6"/>
-      <c r="H226" s="6"/>
-      <c r="I226" s="6"/>
-      <c r="J226" s="6"/>
-      <c r="L226" s="6"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="6"/>
-      <c r="B227" s="6"/>
-      <c r="C227" s="6"/>
-      <c r="D227" s="6"/>
-      <c r="E227" s="6"/>
-      <c r="F227" s="6"/>
-      <c r="G227" s="6"/>
-      <c r="H227" s="6"/>
-      <c r="I227" s="6"/>
-      <c r="J227" s="6"/>
-      <c r="L227" s="6"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="6"/>
-      <c r="B228" s="6"/>
-      <c r="C228" s="6"/>
-      <c r="D228" s="6"/>
-      <c r="E228" s="6"/>
-      <c r="F228" s="6"/>
-      <c r="G228" s="6"/>
-      <c r="H228" s="6"/>
-      <c r="I228" s="6"/>
-      <c r="J228" s="6"/>
-      <c r="L228" s="6"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="6"/>
-      <c r="B229" s="6"/>
-      <c r="C229" s="6"/>
-      <c r="D229" s="6"/>
-      <c r="E229" s="6"/>
-      <c r="F229" s="6"/>
-      <c r="G229" s="6"/>
-      <c r="H229" s="6"/>
-      <c r="I229" s="6"/>
-      <c r="J229" s="6"/>
-      <c r="L229" s="6"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="6"/>
-      <c r="B230" s="6"/>
-      <c r="C230" s="6"/>
-      <c r="D230" s="6"/>
-      <c r="E230" s="6"/>
-      <c r="F230" s="6"/>
-      <c r="G230" s="6"/>
-      <c r="H230" s="6"/>
-      <c r="I230" s="6"/>
-      <c r="J230" s="6"/>
-      <c r="L230" s="6"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="6"/>
-      <c r="B231" s="6"/>
-      <c r="C231" s="6"/>
-      <c r="D231" s="6"/>
-      <c r="E231" s="6"/>
-      <c r="F231" s="6"/>
-      <c r="G231" s="6"/>
-      <c r="H231" s="6"/>
-      <c r="I231" s="6"/>
-      <c r="J231" s="6"/>
-      <c r="L231" s="6"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="6"/>
-      <c r="B232" s="6"/>
-      <c r="C232" s="6"/>
-      <c r="D232" s="6"/>
-      <c r="E232" s="6"/>
-      <c r="F232" s="6"/>
-      <c r="G232" s="6"/>
-      <c r="H232" s="6"/>
-      <c r="I232" s="6"/>
-      <c r="J232" s="6"/>
-      <c r="L232" s="6"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="6"/>
-      <c r="B233" s="6"/>
-      <c r="C233" s="6"/>
-      <c r="D233" s="6"/>
-      <c r="E233" s="6"/>
-      <c r="F233" s="6"/>
-      <c r="G233" s="6"/>
-      <c r="H233" s="6"/>
-      <c r="I233" s="6"/>
-      <c r="J233" s="6"/>
-      <c r="L233" s="6"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="6"/>
-      <c r="B234" s="6"/>
-      <c r="C234" s="6"/>
-      <c r="D234" s="6"/>
-      <c r="E234" s="6"/>
-      <c r="F234" s="6"/>
-      <c r="G234" s="6"/>
-      <c r="H234" s="6"/>
-      <c r="I234" s="6"/>
-      <c r="J234" s="6"/>
-      <c r="L234" s="6"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="6"/>
-      <c r="B235" s="6"/>
-      <c r="C235" s="6"/>
-      <c r="D235" s="6"/>
-      <c r="E235" s="6"/>
-      <c r="F235" s="6"/>
-      <c r="G235" s="6"/>
-      <c r="H235" s="6"/>
-      <c r="I235" s="6"/>
-      <c r="J235" s="6"/>
-      <c r="L235" s="6"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="6"/>
-      <c r="B236" s="6"/>
-      <c r="C236" s="6"/>
-      <c r="D236" s="6"/>
-      <c r="E236" s="6"/>
-      <c r="F236" s="6"/>
-      <c r="G236" s="6"/>
-      <c r="H236" s="6"/>
-      <c r="I236" s="6"/>
-      <c r="J236" s="6"/>
-      <c r="L236" s="6"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="6"/>
-      <c r="B237" s="6"/>
-      <c r="C237" s="6"/>
-      <c r="D237" s="6"/>
-      <c r="E237" s="6"/>
-      <c r="F237" s="6"/>
-      <c r="G237" s="6"/>
-      <c r="H237" s="6"/>
-      <c r="I237" s="6"/>
-      <c r="J237" s="6"/>
-      <c r="L237" s="6"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="6"/>
-      <c r="B238" s="6"/>
-      <c r="C238" s="6"/>
-      <c r="D238" s="6"/>
-      <c r="E238" s="6"/>
-      <c r="F238" s="6"/>
-      <c r="G238" s="6"/>
-      <c r="H238" s="6"/>
-      <c r="I238" s="6"/>
-      <c r="J238" s="6"/>
-      <c r="L238" s="6"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="6"/>
-      <c r="B239" s="6"/>
-      <c r="C239" s="6"/>
-      <c r="D239" s="6"/>
-      <c r="E239" s="6"/>
-      <c r="F239" s="6"/>
-      <c r="G239" s="6"/>
-      <c r="H239" s="6"/>
-      <c r="I239" s="6"/>
-      <c r="J239" s="6"/>
-      <c r="L239" s="6"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="6"/>
-      <c r="B240" s="6"/>
-      <c r="C240" s="6"/>
-      <c r="D240" s="6"/>
-      <c r="E240" s="6"/>
-      <c r="F240" s="6"/>
-      <c r="G240" s="6"/>
-      <c r="H240" s="6"/>
-      <c r="I240" s="6"/>
-      <c r="J240" s="6"/>
-      <c r="L240" s="6"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="6"/>
-      <c r="B241" s="6"/>
-      <c r="C241" s="6"/>
-      <c r="D241" s="6"/>
-      <c r="E241" s="6"/>
-      <c r="F241" s="6"/>
-      <c r="G241" s="6"/>
-      <c r="H241" s="6"/>
-      <c r="I241" s="6"/>
-      <c r="J241" s="6"/>
-      <c r="L241" s="6"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="6"/>
-      <c r="B242" s="6"/>
-      <c r="C242" s="6"/>
-      <c r="D242" s="6"/>
-      <c r="E242" s="6"/>
-      <c r="F242" s="6"/>
-      <c r="G242" s="6"/>
-      <c r="H242" s="6"/>
-      <c r="I242" s="6"/>
-      <c r="J242" s="6"/>
-      <c r="L242" s="6"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="6"/>
-      <c r="B243" s="6"/>
-      <c r="C243" s="6"/>
-      <c r="D243" s="6"/>
-      <c r="E243" s="6"/>
-      <c r="F243" s="6"/>
-      <c r="G243" s="6"/>
-      <c r="H243" s="6"/>
-      <c r="I243" s="6"/>
-      <c r="J243" s="6"/>
-      <c r="L243" s="6"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="6"/>
-      <c r="B244" s="6"/>
-      <c r="C244" s="6"/>
-      <c r="D244" s="6"/>
-      <c r="E244" s="6"/>
-      <c r="F244" s="6"/>
-      <c r="G244" s="6"/>
-      <c r="H244" s="6"/>
-      <c r="I244" s="6"/>
-      <c r="J244" s="6"/>
-      <c r="L244" s="6"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="6"/>
-      <c r="B245" s="6"/>
-      <c r="C245" s="6"/>
-      <c r="D245" s="6"/>
-      <c r="E245" s="6"/>
-      <c r="F245" s="6"/>
-      <c r="G245" s="6"/>
-      <c r="H245" s="6"/>
-      <c r="I245" s="6"/>
-      <c r="J245" s="6"/>
-      <c r="L245" s="6"/>
-    </row>
-    <row r="246">
-      <c r="A246" s="6"/>
-      <c r="B246" s="6"/>
-      <c r="C246" s="6"/>
-      <c r="D246" s="6"/>
-      <c r="E246" s="6"/>
-      <c r="F246" s="6"/>
-      <c r="G246" s="6"/>
-      <c r="H246" s="6"/>
-      <c r="I246" s="6"/>
-      <c r="J246" s="6"/>
-      <c r="L246" s="6"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="6"/>
-      <c r="B247" s="6"/>
-      <c r="C247" s="6"/>
-      <c r="D247" s="6"/>
-      <c r="E247" s="6"/>
-      <c r="F247" s="6"/>
-      <c r="G247" s="6"/>
-      <c r="H247" s="6"/>
-      <c r="I247" s="6"/>
-      <c r="J247" s="6"/>
-      <c r="L247" s="6"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="6"/>
-      <c r="B248" s="6"/>
-      <c r="C248" s="6"/>
-      <c r="D248" s="6"/>
-      <c r="E248" s="6"/>
-      <c r="F248" s="6"/>
-      <c r="G248" s="6"/>
-      <c r="H248" s="6"/>
-      <c r="I248" s="6"/>
-      <c r="J248" s="6"/>
-      <c r="L248" s="6"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="6"/>
-      <c r="B249" s="6"/>
-      <c r="C249" s="6"/>
-      <c r="D249" s="6"/>
-      <c r="E249" s="6"/>
-      <c r="F249" s="6"/>
-      <c r="G249" s="6"/>
-      <c r="H249" s="6"/>
-      <c r="I249" s="6"/>
-      <c r="J249" s="6"/>
-      <c r="L249" s="6"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="6"/>
-      <c r="B250" s="6"/>
-      <c r="C250" s="6"/>
-      <c r="D250" s="6"/>
-      <c r="E250" s="6"/>
-      <c r="F250" s="6"/>
-      <c r="G250" s="6"/>
-      <c r="H250" s="6"/>
-      <c r="I250" s="6"/>
-      <c r="J250" s="6"/>
-      <c r="L250" s="6"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="6"/>
-      <c r="B251" s="6"/>
-      <c r="C251" s="6"/>
-      <c r="D251" s="6"/>
-      <c r="E251" s="6"/>
-      <c r="F251" s="6"/>
-      <c r="G251" s="6"/>
-      <c r="H251" s="6"/>
-      <c r="I251" s="6"/>
-      <c r="J251" s="6"/>
-      <c r="L251" s="6"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="6"/>
-      <c r="B252" s="6"/>
-      <c r="C252" s="6"/>
-      <c r="D252" s="6"/>
-      <c r="E252" s="6"/>
-      <c r="F252" s="6"/>
-      <c r="G252" s="6"/>
-      <c r="H252" s="6"/>
-      <c r="I252" s="6"/>
-      <c r="J252" s="6"/>
-      <c r="L252" s="6"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="6"/>
-      <c r="B253" s="6"/>
-      <c r="C253" s="6"/>
-      <c r="D253" s="6"/>
-      <c r="E253" s="6"/>
-      <c r="F253" s="6"/>
-      <c r="G253" s="6"/>
-      <c r="H253" s="6"/>
-      <c r="I253" s="6"/>
-      <c r="J253" s="6"/>
-      <c r="L253" s="6"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="6"/>
-      <c r="B254" s="6"/>
-      <c r="C254" s="6"/>
-      <c r="D254" s="6"/>
-      <c r="E254" s="6"/>
-      <c r="F254" s="6"/>
-      <c r="G254" s="6"/>
-      <c r="H254" s="6"/>
-      <c r="I254" s="6"/>
-      <c r="J254" s="6"/>
-      <c r="L254" s="6"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="6"/>
-      <c r="B255" s="6"/>
-      <c r="C255" s="6"/>
-      <c r="D255" s="6"/>
-      <c r="E255" s="6"/>
-      <c r="F255" s="6"/>
-      <c r="G255" s="6"/>
-      <c r="H255" s="6"/>
-      <c r="I255" s="6"/>
-      <c r="J255" s="6"/>
-      <c r="L255" s="6"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="6"/>
-      <c r="B256" s="6"/>
-      <c r="C256" s="6"/>
-      <c r="D256" s="6"/>
-      <c r="E256" s="6"/>
-      <c r="F256" s="6"/>
-      <c r="G256" s="6"/>
-      <c r="H256" s="6"/>
-      <c r="I256" s="6"/>
-      <c r="J256" s="6"/>
-      <c r="L256" s="6"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="6"/>
-      <c r="B257" s="6"/>
-      <c r="C257" s="6"/>
-      <c r="D257" s="6"/>
-      <c r="E257" s="6"/>
-      <c r="F257" s="6"/>
-      <c r="G257" s="6"/>
-      <c r="H257" s="6"/>
-      <c r="I257" s="6"/>
-      <c r="J257" s="6"/>
-      <c r="L257" s="6"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="6"/>
-      <c r="B258" s="6"/>
-      <c r="C258" s="6"/>
-      <c r="D258" s="6"/>
-      <c r="E258" s="6"/>
-      <c r="F258" s="6"/>
-      <c r="G258" s="6"/>
-      <c r="H258" s="6"/>
-      <c r="I258" s="6"/>
-      <c r="J258" s="6"/>
-      <c r="L258" s="6"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="6"/>
-      <c r="B259" s="6"/>
-      <c r="C259" s="6"/>
-      <c r="D259" s="6"/>
-      <c r="E259" s="6"/>
-      <c r="F259" s="6"/>
-      <c r="G259" s="6"/>
-      <c r="H259" s="6"/>
-      <c r="I259" s="6"/>
-      <c r="J259" s="6"/>
-      <c r="L259" s="6"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="6"/>
-      <c r="B260" s="6"/>
-      <c r="C260" s="6"/>
-      <c r="D260" s="6"/>
-      <c r="E260" s="6"/>
-      <c r="F260" s="6"/>
-      <c r="G260" s="6"/>
-      <c r="H260" s="6"/>
-      <c r="I260" s="6"/>
-      <c r="J260" s="6"/>
-      <c r="L260" s="6"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="6"/>
-      <c r="B261" s="6"/>
-      <c r="C261" s="6"/>
-      <c r="D261" s="6"/>
-      <c r="E261" s="6"/>
-      <c r="F261" s="6"/>
-      <c r="G261" s="6"/>
-      <c r="H261" s="6"/>
-      <c r="I261" s="6"/>
-      <c r="J261" s="6"/>
-      <c r="L261" s="6"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="6"/>
-      <c r="B262" s="6"/>
-      <c r="C262" s="6"/>
-      <c r="D262" s="6"/>
-      <c r="E262" s="6"/>
-      <c r="F262" s="6"/>
-      <c r="G262" s="6"/>
-      <c r="H262" s="6"/>
-      <c r="I262" s="6"/>
-      <c r="J262" s="6"/>
-      <c r="L262" s="6"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="6"/>
-      <c r="B263" s="6"/>
-      <c r="C263" s="6"/>
-      <c r="D263" s="6"/>
-      <c r="E263" s="6"/>
-      <c r="F263" s="6"/>
-      <c r="G263" s="6"/>
-      <c r="H263" s="6"/>
-      <c r="I263" s="6"/>
-      <c r="J263" s="6"/>
-      <c r="L263" s="6"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="6"/>
-      <c r="B264" s="6"/>
-      <c r="C264" s="6"/>
-      <c r="D264" s="6"/>
-      <c r="E264" s="6"/>
-      <c r="F264" s="6"/>
-      <c r="G264" s="6"/>
-      <c r="H264" s="6"/>
-      <c r="I264" s="6"/>
-      <c r="J264" s="6"/>
-      <c r="L264" s="6"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
+      <c r="E107" s="1"/>
+      <c r="F107" s="1"/>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="1"/>
+      <c r="J107" s="1"/>
+      <c r="L107" s="1"/>
+      <c r="M107" s="7"/>
+      <c r="N107" s="7"/>
+      <c r="O107" s="7"/>
+    </row>
+    <row r="108" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
+      <c r="D108" s="1"/>
+      <c r="E108" s="1"/>
+      <c r="F108" s="1"/>
+      <c r="G108" s="1"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1"/>
+      <c r="L108" s="1"/>
+      <c r="M108" s="7"/>
+      <c r="N108" s="7"/>
+      <c r="O108" s="7"/>
+    </row>
+    <row r="109" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1"/>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1"/>
+      <c r="L109" s="1"/>
+      <c r="M109" s="7"/>
+      <c r="N109" s="7"/>
+      <c r="O109" s="7"/>
+    </row>
+    <row r="110" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A110" s="1"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1"/>
+      <c r="L110" s="1"/>
+      <c r="M110" s="7"/>
+      <c r="N110" s="7"/>
+      <c r="O110" s="7"/>
+    </row>
+    <row r="111" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A111" s="1"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
+      <c r="L111" s="1"/>
+      <c r="M111" s="7"/>
+      <c r="N111" s="7"/>
+      <c r="O111" s="7"/>
+    </row>
+    <row r="112" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1"/>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1"/>
+      <c r="L112" s="1"/>
+      <c r="M112" s="7"/>
+      <c r="N112" s="7"/>
+      <c r="O112" s="7"/>
+    </row>
+    <row r="113" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1"/>
+      <c r="L113" s="1"/>
+      <c r="M113" s="7"/>
+      <c r="N113" s="7"/>
+      <c r="O113" s="7"/>
+    </row>
+    <row r="114" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A114" s="1"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
+      <c r="E114" s="1"/>
+      <c r="F114" s="1"/>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1"/>
+      <c r="L114" s="1"/>
+      <c r="M114" s="7"/>
+      <c r="N114" s="7"/>
+      <c r="O114" s="7"/>
+    </row>
+    <row r="115" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
+      <c r="E115" s="1"/>
+      <c r="F115" s="1"/>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1"/>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1"/>
+      <c r="L115" s="1"/>
+      <c r="M115" s="7"/>
+      <c r="N115" s="7"/>
+      <c r="O115" s="7"/>
+    </row>
+    <row r="116" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A116" s="1"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
+      <c r="E116" s="1"/>
+      <c r="F116" s="1"/>
+      <c r="G116" s="1"/>
+      <c r="H116" s="1"/>
+      <c r="I116" s="1"/>
+      <c r="J116" s="1"/>
+      <c r="L116" s="1"/>
+      <c r="M116" s="7"/>
+      <c r="N116" s="7"/>
+      <c r="O116" s="7"/>
+    </row>
+    <row r="117" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A117" s="1"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
+      <c r="E117" s="1"/>
+      <c r="F117" s="1"/>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1"/>
+      <c r="L117" s="1"/>
+      <c r="M117" s="7"/>
+      <c r="N117" s="7"/>
+      <c r="O117" s="7"/>
+    </row>
+    <row r="118" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A118" s="1"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
+      <c r="E118" s="1"/>
+      <c r="F118" s="1"/>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1"/>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1"/>
+      <c r="L118" s="1"/>
+      <c r="M118" s="7"/>
+      <c r="N118" s="7"/>
+      <c r="O118" s="7"/>
+    </row>
+    <row r="119" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A119" s="1"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
+      <c r="E119" s="1"/>
+      <c r="F119" s="1"/>
+      <c r="G119" s="1"/>
+      <c r="H119" s="1"/>
+      <c r="I119" s="1"/>
+      <c r="J119" s="1"/>
+      <c r="L119" s="1"/>
+      <c r="M119" s="7"/>
+      <c r="N119" s="7"/>
+      <c r="O119" s="7"/>
+    </row>
+    <row r="120" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A120" s="1"/>
+      <c r="B120" s="1"/>
+      <c r="C120" s="1"/>
+      <c r="D120" s="1"/>
+      <c r="E120" s="1"/>
+      <c r="F120" s="1"/>
+      <c r="G120" s="1"/>
+      <c r="H120" s="1"/>
+      <c r="I120" s="1"/>
+      <c r="J120" s="1"/>
+      <c r="L120" s="1"/>
+      <c r="M120" s="7"/>
+      <c r="N120" s="7"/>
+      <c r="O120" s="7"/>
+    </row>
+    <row r="121" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A121" s="1"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
+      <c r="E121" s="1"/>
+      <c r="F121" s="1"/>
+      <c r="G121" s="1"/>
+      <c r="H121" s="1"/>
+      <c r="I121" s="1"/>
+      <c r="J121" s="1"/>
+      <c r="L121" s="1"/>
+      <c r="M121" s="7"/>
+      <c r="N121" s="7"/>
+      <c r="O121" s="7"/>
+    </row>
+    <row r="122" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
+      <c r="E122" s="1"/>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1"/>
+      <c r="L122" s="1"/>
+      <c r="M122" s="7"/>
+      <c r="N122" s="7"/>
+      <c r="O122" s="7"/>
+    </row>
+    <row r="123" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A123" s="1"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
+      <c r="E123" s="1"/>
+      <c r="F123" s="1"/>
+      <c r="G123" s="1"/>
+      <c r="H123" s="1"/>
+      <c r="I123" s="1"/>
+      <c r="J123" s="1"/>
+      <c r="L123" s="1"/>
+      <c r="M123" s="7"/>
+      <c r="N123" s="7"/>
+      <c r="O123" s="7"/>
+    </row>
+    <row r="124" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A124" s="1"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
+      <c r="E124" s="1"/>
+      <c r="F124" s="1"/>
+      <c r="G124" s="1"/>
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
+      <c r="J124" s="1"/>
+      <c r="L124" s="1"/>
+      <c r="M124" s="7"/>
+      <c r="N124" s="7"/>
+      <c r="O124" s="7"/>
+    </row>
+    <row r="125" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A125" s="1"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
+      <c r="E125" s="1"/>
+      <c r="F125" s="1"/>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1"/>
+      <c r="I125" s="1"/>
+      <c r="J125" s="1"/>
+      <c r="L125" s="1"/>
+      <c r="M125" s="7"/>
+      <c r="N125" s="7"/>
+      <c r="O125" s="7"/>
+    </row>
+    <row r="126" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A126" s="1"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
+      <c r="E126" s="1"/>
+      <c r="F126" s="1"/>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1"/>
+      <c r="L126" s="1"/>
+      <c r="M126" s="7"/>
+      <c r="N126" s="7"/>
+      <c r="O126" s="7"/>
+    </row>
+    <row r="127" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A127" s="1"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="D127" s="1"/>
+      <c r="E127" s="1"/>
+      <c r="F127" s="1"/>
+      <c r="G127" s="1"/>
+      <c r="H127" s="1"/>
+      <c r="I127" s="1"/>
+      <c r="J127" s="1"/>
+      <c r="L127" s="1"/>
+      <c r="M127" s="7"/>
+      <c r="N127" s="7"/>
+      <c r="O127" s="7"/>
+    </row>
+    <row r="128" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A128" s="1"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
+      <c r="E128" s="1"/>
+      <c r="F128" s="1"/>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1"/>
+      <c r="L128" s="1"/>
+      <c r="M128" s="7"/>
+      <c r="N128" s="7"/>
+      <c r="O128" s="7"/>
+    </row>
+    <row r="129" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A129" s="1"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1"/>
+      <c r="L129" s="1"/>
+      <c r="M129" s="7"/>
+      <c r="N129" s="7"/>
+      <c r="O129" s="7"/>
+    </row>
+    <row r="130" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A130" s="1"/>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="1"/>
+      <c r="E130" s="1"/>
+      <c r="F130" s="1"/>
+      <c r="G130" s="1"/>
+      <c r="H130" s="1"/>
+      <c r="I130" s="1"/>
+      <c r="J130" s="1"/>
+      <c r="L130" s="1"/>
+      <c r="M130" s="7"/>
+      <c r="N130" s="7"/>
+      <c r="O130" s="7"/>
+    </row>
+    <row r="131" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A131" s="1"/>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
+      <c r="E131" s="1"/>
+      <c r="F131" s="1"/>
+      <c r="G131" s="1"/>
+      <c r="H131" s="1"/>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1"/>
+      <c r="L131" s="1"/>
+      <c r="M131" s="7"/>
+      <c r="N131" s="7"/>
+      <c r="O131" s="7"/>
+    </row>
+    <row r="132" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A132" s="1"/>
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
+      <c r="E132" s="1"/>
+      <c r="F132" s="1"/>
+      <c r="G132" s="1"/>
+      <c r="H132" s="1"/>
+      <c r="I132" s="1"/>
+      <c r="J132" s="1"/>
+      <c r="L132" s="1"/>
+      <c r="M132" s="7"/>
+      <c r="N132" s="7"/>
+      <c r="O132" s="7"/>
+    </row>
+    <row r="133" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A133" s="1"/>
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
+      <c r="E133" s="1"/>
+      <c r="F133" s="1"/>
+      <c r="G133" s="1"/>
+      <c r="H133" s="1"/>
+      <c r="I133" s="1"/>
+      <c r="J133" s="1"/>
+      <c r="L133" s="1"/>
+      <c r="M133" s="7"/>
+      <c r="N133" s="7"/>
+      <c r="O133" s="7"/>
+    </row>
+    <row r="134" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A134" s="1"/>
+      <c r="B134" s="1"/>
+      <c r="C134" s="1"/>
+      <c r="D134" s="1"/>
+      <c r="E134" s="1"/>
+      <c r="F134" s="1"/>
+      <c r="G134" s="1"/>
+      <c r="H134" s="1"/>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1"/>
+      <c r="L134" s="1"/>
+      <c r="M134" s="7"/>
+      <c r="N134" s="7"/>
+      <c r="O134" s="7"/>
+    </row>
+    <row r="135" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A135" s="1"/>
+      <c r="B135" s="1"/>
+      <c r="C135" s="1"/>
+      <c r="D135" s="1"/>
+      <c r="E135" s="1"/>
+      <c r="F135" s="1"/>
+      <c r="G135" s="1"/>
+      <c r="H135" s="1"/>
+      <c r="I135" s="1"/>
+      <c r="J135" s="1"/>
+      <c r="L135" s="1"/>
+      <c r="M135" s="7"/>
+      <c r="N135" s="7"/>
+      <c r="O135" s="7"/>
+    </row>
+    <row r="136" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A136" s="1"/>
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
+      <c r="E136" s="1"/>
+      <c r="F136" s="1"/>
+      <c r="G136" s="1"/>
+      <c r="H136" s="1"/>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1"/>
+      <c r="L136" s="1"/>
+      <c r="M136" s="7"/>
+      <c r="N136" s="7"/>
+      <c r="O136" s="7"/>
+    </row>
+    <row r="137" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A137" s="1"/>
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
+      <c r="D137" s="1"/>
+      <c r="E137" s="1"/>
+      <c r="F137" s="1"/>
+      <c r="G137" s="1"/>
+      <c r="H137" s="1"/>
+      <c r="I137" s="1"/>
+      <c r="J137" s="1"/>
+      <c r="L137" s="1"/>
+      <c r="M137" s="7"/>
+      <c r="N137" s="7"/>
+      <c r="O137" s="7"/>
+    </row>
+    <row r="138" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A138" s="1"/>
+      <c r="B138" s="1"/>
+      <c r="C138" s="1"/>
+      <c r="D138" s="1"/>
+      <c r="E138" s="1"/>
+      <c r="F138" s="1"/>
+      <c r="G138" s="1"/>
+      <c r="H138" s="1"/>
+      <c r="I138" s="1"/>
+      <c r="J138" s="1"/>
+      <c r="L138" s="1"/>
+      <c r="M138" s="7"/>
+      <c r="N138" s="7"/>
+      <c r="O138" s="7"/>
+    </row>
+    <row r="139" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A139" s="1"/>
+      <c r="B139" s="1"/>
+      <c r="C139" s="1"/>
+      <c r="D139" s="1"/>
+      <c r="E139" s="1"/>
+      <c r="F139" s="1"/>
+      <c r="G139" s="1"/>
+      <c r="H139" s="1"/>
+      <c r="I139" s="1"/>
+      <c r="J139" s="1"/>
+      <c r="L139" s="1"/>
+      <c r="M139" s="7"/>
+      <c r="N139" s="7"/>
+      <c r="O139" s="7"/>
+    </row>
+    <row r="140" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A140" s="1"/>
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
+      <c r="D140" s="1"/>
+      <c r="E140" s="1"/>
+      <c r="F140" s="1"/>
+      <c r="G140" s="1"/>
+      <c r="H140" s="1"/>
+      <c r="I140" s="1"/>
+      <c r="J140" s="1"/>
+      <c r="L140" s="1"/>
+      <c r="M140" s="7"/>
+      <c r="N140" s="7"/>
+      <c r="O140" s="7"/>
+    </row>
+    <row r="141" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A141" s="1"/>
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
+      <c r="D141" s="1"/>
+      <c r="E141" s="1"/>
+      <c r="F141" s="1"/>
+      <c r="G141" s="1"/>
+      <c r="H141" s="1"/>
+      <c r="I141" s="1"/>
+      <c r="J141" s="1"/>
+      <c r="L141" s="1"/>
+      <c r="M141" s="7"/>
+      <c r="N141" s="7"/>
+      <c r="O141" s="7"/>
+    </row>
+    <row r="142" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A142" s="1"/>
+      <c r="B142" s="1"/>
+      <c r="C142" s="1"/>
+      <c r="D142" s="1"/>
+      <c r="E142" s="1"/>
+      <c r="F142" s="1"/>
+      <c r="G142" s="1"/>
+      <c r="H142" s="1"/>
+      <c r="I142" s="1"/>
+      <c r="J142" s="1"/>
+      <c r="L142" s="1"/>
+      <c r="M142" s="7"/>
+      <c r="N142" s="7"/>
+      <c r="O142" s="7"/>
+    </row>
+    <row r="143" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A143" s="1"/>
+      <c r="B143" s="1"/>
+      <c r="C143" s="1"/>
+      <c r="D143" s="1"/>
+      <c r="E143" s="1"/>
+      <c r="F143" s="1"/>
+      <c r="G143" s="1"/>
+      <c r="H143" s="1"/>
+      <c r="I143" s="1"/>
+      <c r="J143" s="1"/>
+      <c r="L143" s="1"/>
+      <c r="M143" s="7"/>
+      <c r="N143" s="7"/>
+      <c r="O143" s="7"/>
+    </row>
+    <row r="144" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A144" s="1"/>
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
+      <c r="D144" s="1"/>
+      <c r="E144" s="1"/>
+      <c r="F144" s="1"/>
+      <c r="G144" s="1"/>
+      <c r="H144" s="1"/>
+      <c r="I144" s="1"/>
+      <c r="J144" s="1"/>
+      <c r="L144" s="1"/>
+      <c r="M144" s="7"/>
+      <c r="N144" s="7"/>
+      <c r="O144" s="7"/>
+    </row>
+    <row r="145" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A145" s="1"/>
+      <c r="B145" s="1"/>
+      <c r="C145" s="1"/>
+      <c r="D145" s="1"/>
+      <c r="E145" s="1"/>
+      <c r="F145" s="1"/>
+      <c r="G145" s="1"/>
+      <c r="H145" s="1"/>
+      <c r="I145" s="1"/>
+      <c r="J145" s="1"/>
+      <c r="L145" s="1"/>
+      <c r="M145" s="7"/>
+      <c r="N145" s="7"/>
+      <c r="O145" s="7"/>
+    </row>
+    <row r="146" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A146" s="1"/>
+      <c r="B146" s="1"/>
+      <c r="C146" s="1"/>
+      <c r="D146" s="1"/>
+      <c r="E146" s="1"/>
+      <c r="F146" s="1"/>
+      <c r="G146" s="1"/>
+      <c r="H146" s="1"/>
+      <c r="I146" s="1"/>
+      <c r="J146" s="1"/>
+      <c r="L146" s="1"/>
+      <c r="M146" s="7"/>
+      <c r="N146" s="7"/>
+      <c r="O146" s="7"/>
+    </row>
+    <row r="147" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A147" s="1"/>
+      <c r="B147" s="1"/>
+      <c r="C147" s="1"/>
+      <c r="D147" s="1"/>
+      <c r="E147" s="1"/>
+      <c r="F147" s="1"/>
+      <c r="G147" s="1"/>
+      <c r="H147" s="1"/>
+      <c r="I147" s="1"/>
+      <c r="J147" s="1"/>
+      <c r="L147" s="1"/>
+      <c r="M147" s="7"/>
+      <c r="N147" s="7"/>
+      <c r="O147" s="7"/>
+    </row>
+    <row r="148" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A148" s="1"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
+      <c r="E148" s="1"/>
+      <c r="F148" s="1"/>
+      <c r="G148" s="1"/>
+      <c r="H148" s="1"/>
+      <c r="I148" s="1"/>
+      <c r="J148" s="1"/>
+      <c r="L148" s="1"/>
+      <c r="M148" s="7"/>
+      <c r="N148" s="7"/>
+      <c r="O148" s="7"/>
+    </row>
+    <row r="149" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A149" s="1"/>
+      <c r="B149" s="1"/>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1"/>
+      <c r="E149" s="1"/>
+      <c r="F149" s="1"/>
+      <c r="G149" s="1"/>
+      <c r="H149" s="1"/>
+      <c r="I149" s="1"/>
+      <c r="J149" s="1"/>
+      <c r="L149" s="1"/>
+      <c r="M149" s="7"/>
+      <c r="N149" s="7"/>
+      <c r="O149" s="7"/>
+    </row>
+    <row r="150" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A150" s="1"/>
+      <c r="B150" s="1"/>
+      <c r="C150" s="1"/>
+      <c r="D150" s="1"/>
+      <c r="E150" s="1"/>
+      <c r="F150" s="1"/>
+      <c r="G150" s="1"/>
+      <c r="H150" s="1"/>
+      <c r="I150" s="1"/>
+      <c r="J150" s="1"/>
+      <c r="L150" s="1"/>
+      <c r="M150" s="7"/>
+      <c r="N150" s="7"/>
+      <c r="O150" s="7"/>
+    </row>
+    <row r="151" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A151" s="1"/>
+      <c r="B151" s="1"/>
+      <c r="C151" s="1"/>
+      <c r="D151" s="1"/>
+      <c r="E151" s="1"/>
+      <c r="F151" s="1"/>
+      <c r="G151" s="1"/>
+      <c r="H151" s="1"/>
+      <c r="I151" s="1"/>
+      <c r="J151" s="1"/>
+      <c r="L151" s="1"/>
+      <c r="M151" s="7"/>
+      <c r="N151" s="7"/>
+      <c r="O151" s="7"/>
+    </row>
+    <row r="152" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A152" s="1"/>
+      <c r="B152" s="1"/>
+      <c r="C152" s="1"/>
+      <c r="D152" s="1"/>
+      <c r="E152" s="1"/>
+      <c r="F152" s="1"/>
+      <c r="G152" s="1"/>
+      <c r="H152" s="1"/>
+      <c r="I152" s="1"/>
+      <c r="J152" s="1"/>
+      <c r="L152" s="1"/>
+    </row>
+    <row r="153" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A153" s="1"/>
+      <c r="B153" s="1"/>
+      <c r="C153" s="1"/>
+      <c r="D153" s="1"/>
+      <c r="E153" s="1"/>
+      <c r="F153" s="1"/>
+      <c r="G153" s="1"/>
+      <c r="H153" s="1"/>
+      <c r="I153" s="1"/>
+      <c r="J153" s="1"/>
+      <c r="L153" s="1"/>
+    </row>
+    <row r="154" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A154" s="1"/>
+      <c r="B154" s="1"/>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1"/>
+      <c r="E154" s="1"/>
+      <c r="F154" s="1"/>
+      <c r="G154" s="1"/>
+      <c r="H154" s="1"/>
+      <c r="I154" s="1"/>
+      <c r="J154" s="1"/>
+      <c r="L154" s="1"/>
+    </row>
+    <row r="155" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A155" s="1"/>
+      <c r="B155" s="1"/>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1"/>
+      <c r="E155" s="1"/>
+      <c r="F155" s="1"/>
+      <c r="G155" s="1"/>
+      <c r="H155" s="1"/>
+      <c r="I155" s="1"/>
+      <c r="J155" s="1"/>
+      <c r="L155" s="1"/>
+    </row>
+    <row r="156" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A156" s="1"/>
+      <c r="B156" s="1"/>
+      <c r="C156" s="1"/>
+      <c r="D156" s="1"/>
+      <c r="E156" s="1"/>
+      <c r="F156" s="1"/>
+      <c r="G156" s="1"/>
+      <c r="H156" s="1"/>
+      <c r="I156" s="1"/>
+      <c r="J156" s="1"/>
+      <c r="L156" s="1"/>
+    </row>
+    <row r="157" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A157" s="1"/>
+      <c r="B157" s="1"/>
+      <c r="C157" s="1"/>
+      <c r="D157" s="1"/>
+      <c r="E157" s="1"/>
+      <c r="F157" s="1"/>
+      <c r="G157" s="1"/>
+      <c r="H157" s="1"/>
+      <c r="I157" s="1"/>
+      <c r="J157" s="1"/>
+      <c r="L157" s="1"/>
+    </row>
+    <row r="158" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A158" s="1"/>
+      <c r="B158" s="1"/>
+      <c r="C158" s="1"/>
+      <c r="D158" s="1"/>
+      <c r="E158" s="1"/>
+      <c r="F158" s="1"/>
+      <c r="G158" s="1"/>
+      <c r="H158" s="1"/>
+      <c r="I158" s="1"/>
+      <c r="J158" s="1"/>
+      <c r="L158" s="1"/>
+    </row>
+    <row r="159" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A159" s="1"/>
+      <c r="B159" s="1"/>
+      <c r="C159" s="1"/>
+      <c r="D159" s="1"/>
+      <c r="E159" s="1"/>
+      <c r="F159" s="1"/>
+      <c r="G159" s="1"/>
+      <c r="H159" s="1"/>
+      <c r="I159" s="1"/>
+      <c r="J159" s="1"/>
+      <c r="L159" s="1"/>
+    </row>
+    <row r="160" spans="1:15" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A160" s="1"/>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
+      <c r="E160" s="1"/>
+      <c r="F160" s="1"/>
+      <c r="G160" s="1"/>
+      <c r="H160" s="1"/>
+      <c r="I160" s="1"/>
+      <c r="J160" s="1"/>
+      <c r="L160" s="1"/>
+    </row>
+    <row r="161" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A161" s="1"/>
+      <c r="B161" s="1"/>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
+      <c r="E161" s="1"/>
+      <c r="F161" s="1"/>
+      <c r="G161" s="1"/>
+      <c r="H161" s="1"/>
+      <c r="I161" s="1"/>
+      <c r="J161" s="1"/>
+      <c r="L161" s="1"/>
+    </row>
+    <row r="162" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A162" s="1"/>
+      <c r="B162" s="1"/>
+      <c r="C162" s="1"/>
+      <c r="D162" s="1"/>
+      <c r="E162" s="1"/>
+      <c r="F162" s="1"/>
+      <c r="G162" s="1"/>
+      <c r="H162" s="1"/>
+      <c r="I162" s="1"/>
+      <c r="J162" s="1"/>
+      <c r="L162" s="1"/>
+    </row>
+    <row r="163" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A163" s="1"/>
+      <c r="B163" s="1"/>
+      <c r="C163" s="1"/>
+      <c r="D163" s="1"/>
+      <c r="E163" s="1"/>
+      <c r="F163" s="1"/>
+      <c r="G163" s="1"/>
+      <c r="H163" s="1"/>
+      <c r="I163" s="1"/>
+      <c r="J163" s="1"/>
+      <c r="L163" s="1"/>
+    </row>
+    <row r="164" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A164" s="1"/>
+      <c r="B164" s="1"/>
+      <c r="C164" s="1"/>
+      <c r="D164" s="1"/>
+      <c r="E164" s="1"/>
+      <c r="F164" s="1"/>
+      <c r="G164" s="1"/>
+      <c r="H164" s="1"/>
+      <c r="I164" s="1"/>
+      <c r="J164" s="1"/>
+      <c r="L164" s="1"/>
+    </row>
+    <row r="165" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A165" s="1"/>
+      <c r="B165" s="1"/>
+      <c r="C165" s="1"/>
+      <c r="D165" s="1"/>
+      <c r="E165" s="1"/>
+      <c r="F165" s="1"/>
+      <c r="G165" s="1"/>
+      <c r="H165" s="1"/>
+      <c r="I165" s="1"/>
+      <c r="J165" s="1"/>
+      <c r="L165" s="1"/>
+    </row>
+    <row r="166" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A166" s="1"/>
+      <c r="B166" s="1"/>
+      <c r="C166" s="1"/>
+      <c r="D166" s="1"/>
+      <c r="E166" s="1"/>
+      <c r="F166" s="1"/>
+      <c r="G166" s="1"/>
+      <c r="H166" s="1"/>
+      <c r="I166" s="1"/>
+      <c r="J166" s="1"/>
+      <c r="L166" s="1"/>
+    </row>
+    <row r="167" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A167" s="1"/>
+      <c r="B167" s="1"/>
+      <c r="C167" s="1"/>
+      <c r="D167" s="1"/>
+      <c r="E167" s="1"/>
+      <c r="F167" s="1"/>
+      <c r="G167" s="1"/>
+      <c r="H167" s="1"/>
+      <c r="I167" s="1"/>
+      <c r="J167" s="1"/>
+      <c r="L167" s="1"/>
+    </row>
+    <row r="168" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A168" s="1"/>
+      <c r="B168" s="1"/>
+      <c r="C168" s="1"/>
+      <c r="D168" s="1"/>
+      <c r="E168" s="1"/>
+      <c r="F168" s="1"/>
+      <c r="G168" s="1"/>
+      <c r="H168" s="1"/>
+      <c r="I168" s="1"/>
+      <c r="J168" s="1"/>
+      <c r="L168" s="1"/>
+    </row>
+    <row r="169" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A169" s="1"/>
+      <c r="B169" s="1"/>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
+      <c r="E169" s="1"/>
+      <c r="F169" s="1"/>
+      <c r="G169" s="1"/>
+      <c r="H169" s="1"/>
+      <c r="I169" s="1"/>
+      <c r="J169" s="1"/>
+      <c r="L169" s="1"/>
+    </row>
+    <row r="170" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A170" s="1"/>
+      <c r="B170" s="1"/>
+      <c r="C170" s="1"/>
+      <c r="D170" s="1"/>
+      <c r="E170" s="1"/>
+      <c r="F170" s="1"/>
+      <c r="G170" s="1"/>
+      <c r="H170" s="1"/>
+      <c r="I170" s="1"/>
+      <c r="J170" s="1"/>
+      <c r="L170" s="1"/>
+    </row>
+    <row r="171" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A171" s="1"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="1"/>
+      <c r="D171" s="1"/>
+      <c r="E171" s="1"/>
+      <c r="F171" s="1"/>
+      <c r="G171" s="1"/>
+      <c r="H171" s="1"/>
+      <c r="I171" s="1"/>
+      <c r="J171" s="1"/>
+      <c r="L171" s="1"/>
+    </row>
+    <row r="172" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A172" s="1"/>
+      <c r="B172" s="1"/>
+      <c r="C172" s="1"/>
+      <c r="D172" s="1"/>
+      <c r="E172" s="1"/>
+      <c r="F172" s="1"/>
+      <c r="G172" s="1"/>
+      <c r="H172" s="1"/>
+      <c r="I172" s="1"/>
+      <c r="J172" s="1"/>
+      <c r="L172" s="1"/>
+    </row>
+    <row r="173" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A173" s="1"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="1"/>
+      <c r="D173" s="1"/>
+      <c r="E173" s="1"/>
+      <c r="F173" s="1"/>
+      <c r="G173" s="1"/>
+      <c r="H173" s="1"/>
+      <c r="I173" s="1"/>
+      <c r="J173" s="1"/>
+      <c r="L173" s="1"/>
+    </row>
+    <row r="174" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A174" s="1"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="1"/>
+      <c r="D174" s="1"/>
+      <c r="E174" s="1"/>
+      <c r="F174" s="1"/>
+      <c r="G174" s="1"/>
+      <c r="H174" s="1"/>
+      <c r="I174" s="1"/>
+      <c r="J174" s="1"/>
+      <c r="L174" s="1"/>
+    </row>
+    <row r="175" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A175" s="1"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
+      <c r="D175" s="1"/>
+      <c r="E175" s="1"/>
+      <c r="F175" s="1"/>
+      <c r="G175" s="1"/>
+      <c r="H175" s="1"/>
+      <c r="I175" s="1"/>
+      <c r="J175" s="1"/>
+      <c r="L175" s="1"/>
+    </row>
+    <row r="176" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A176" s="1"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="1"/>
+      <c r="D176" s="1"/>
+      <c r="E176" s="1"/>
+      <c r="F176" s="1"/>
+      <c r="G176" s="1"/>
+      <c r="H176" s="1"/>
+      <c r="I176" s="1"/>
+      <c r="J176" s="1"/>
+      <c r="L176" s="1"/>
+    </row>
+    <row r="177" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A177" s="1"/>
+      <c r="B177" s="1"/>
+      <c r="C177" s="1"/>
+      <c r="D177" s="1"/>
+      <c r="E177" s="1"/>
+      <c r="F177" s="1"/>
+      <c r="G177" s="1"/>
+      <c r="H177" s="1"/>
+      <c r="I177" s="1"/>
+      <c r="J177" s="1"/>
+      <c r="L177" s="1"/>
+    </row>
+    <row r="178" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A178" s="1"/>
+      <c r="B178" s="1"/>
+      <c r="C178" s="1"/>
+      <c r="D178" s="1"/>
+      <c r="E178" s="1"/>
+      <c r="F178" s="1"/>
+      <c r="G178" s="1"/>
+      <c r="H178" s="1"/>
+      <c r="I178" s="1"/>
+      <c r="J178" s="1"/>
+      <c r="L178" s="1"/>
+    </row>
+    <row r="179" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A179" s="1"/>
+      <c r="B179" s="1"/>
+      <c r="C179" s="1"/>
+      <c r="D179" s="1"/>
+      <c r="E179" s="1"/>
+      <c r="F179" s="1"/>
+      <c r="G179" s="1"/>
+      <c r="H179" s="1"/>
+      <c r="I179" s="1"/>
+      <c r="J179" s="1"/>
+      <c r="L179" s="1"/>
+    </row>
+    <row r="180" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A180" s="1"/>
+      <c r="B180" s="1"/>
+      <c r="C180" s="1"/>
+      <c r="D180" s="1"/>
+      <c r="E180" s="1"/>
+      <c r="F180" s="1"/>
+      <c r="G180" s="1"/>
+      <c r="H180" s="1"/>
+      <c r="I180" s="1"/>
+      <c r="J180" s="1"/>
+      <c r="L180" s="1"/>
+    </row>
+    <row r="181" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A181" s="1"/>
+      <c r="B181" s="1"/>
+      <c r="C181" s="1"/>
+      <c r="D181" s="1"/>
+      <c r="E181" s="1"/>
+      <c r="F181" s="1"/>
+      <c r="G181" s="1"/>
+      <c r="H181" s="1"/>
+      <c r="I181" s="1"/>
+      <c r="J181" s="1"/>
+      <c r="L181" s="1"/>
+    </row>
+    <row r="182" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A182" s="1"/>
+      <c r="B182" s="1"/>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1"/>
+      <c r="E182" s="1"/>
+      <c r="F182" s="1"/>
+      <c r="G182" s="1"/>
+      <c r="H182" s="1"/>
+      <c r="I182" s="1"/>
+      <c r="J182" s="1"/>
+      <c r="L182" s="1"/>
+    </row>
+    <row r="183" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A183" s="1"/>
+      <c r="B183" s="1"/>
+      <c r="C183" s="1"/>
+      <c r="D183" s="1"/>
+      <c r="E183" s="1"/>
+      <c r="F183" s="1"/>
+      <c r="G183" s="1"/>
+      <c r="H183" s="1"/>
+      <c r="I183" s="1"/>
+      <c r="J183" s="1"/>
+      <c r="L183" s="1"/>
+    </row>
+    <row r="184" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A184" s="1"/>
+      <c r="B184" s="1"/>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
+      <c r="E184" s="1"/>
+      <c r="F184" s="1"/>
+      <c r="G184" s="1"/>
+      <c r="H184" s="1"/>
+      <c r="I184" s="1"/>
+      <c r="J184" s="1"/>
+      <c r="L184" s="1"/>
+    </row>
+    <row r="185" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A185" s="1"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="1"/>
+      <c r="D185" s="1"/>
+      <c r="E185" s="1"/>
+      <c r="F185" s="1"/>
+      <c r="G185" s="1"/>
+      <c r="H185" s="1"/>
+      <c r="I185" s="1"/>
+      <c r="J185" s="1"/>
+      <c r="L185" s="1"/>
+    </row>
+    <row r="186" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A186" s="1"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="1"/>
+      <c r="D186" s="1"/>
+      <c r="E186" s="1"/>
+      <c r="F186" s="1"/>
+      <c r="G186" s="1"/>
+      <c r="H186" s="1"/>
+      <c r="I186" s="1"/>
+      <c r="J186" s="1"/>
+      <c r="L186" s="1"/>
+    </row>
+    <row r="187" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A187" s="1"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="1"/>
+      <c r="D187" s="1"/>
+      <c r="E187" s="1"/>
+      <c r="F187" s="1"/>
+      <c r="G187" s="1"/>
+      <c r="H187" s="1"/>
+      <c r="I187" s="1"/>
+      <c r="J187" s="1"/>
+      <c r="L187" s="1"/>
+    </row>
+    <row r="188" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A188" s="1"/>
+      <c r="B188" s="1"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="1"/>
+      <c r="E188" s="1"/>
+      <c r="F188" s="1"/>
+      <c r="G188" s="1"/>
+      <c r="H188" s="1"/>
+      <c r="I188" s="1"/>
+      <c r="J188" s="1"/>
+      <c r="L188" s="1"/>
+    </row>
+    <row r="189" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A189" s="1"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="1"/>
+      <c r="D189" s="1"/>
+      <c r="E189" s="1"/>
+      <c r="F189" s="1"/>
+      <c r="G189" s="1"/>
+      <c r="H189" s="1"/>
+      <c r="I189" s="1"/>
+      <c r="J189" s="1"/>
+      <c r="L189" s="1"/>
+    </row>
+    <row r="190" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A190" s="1"/>
+      <c r="B190" s="1"/>
+      <c r="C190" s="1"/>
+      <c r="D190" s="1"/>
+      <c r="E190" s="1"/>
+      <c r="F190" s="1"/>
+      <c r="G190" s="1"/>
+      <c r="H190" s="1"/>
+      <c r="I190" s="1"/>
+      <c r="J190" s="1"/>
+      <c r="L190" s="1"/>
+    </row>
+    <row r="191" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A191" s="1"/>
+      <c r="B191" s="1"/>
+      <c r="C191" s="1"/>
+      <c r="D191" s="1"/>
+      <c r="E191" s="1"/>
+      <c r="F191" s="1"/>
+      <c r="G191" s="1"/>
+      <c r="H191" s="1"/>
+      <c r="I191" s="1"/>
+      <c r="J191" s="1"/>
+      <c r="L191" s="1"/>
+    </row>
+    <row r="192" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A192" s="1"/>
+      <c r="B192" s="1"/>
+      <c r="C192" s="1"/>
+      <c r="D192" s="1"/>
+      <c r="E192" s="1"/>
+      <c r="F192" s="1"/>
+      <c r="G192" s="1"/>
+      <c r="H192" s="1"/>
+      <c r="I192" s="1"/>
+      <c r="J192" s="1"/>
+      <c r="L192" s="1"/>
+    </row>
+    <row r="193" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A193" s="1"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="1"/>
+      <c r="D193" s="1"/>
+      <c r="E193" s="1"/>
+      <c r="F193" s="1"/>
+      <c r="G193" s="1"/>
+      <c r="H193" s="1"/>
+      <c r="I193" s="1"/>
+      <c r="J193" s="1"/>
+      <c r="L193" s="1"/>
+    </row>
+    <row r="194" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A194" s="1"/>
+      <c r="B194" s="1"/>
+      <c r="C194" s="1"/>
+      <c r="D194" s="1"/>
+      <c r="E194" s="1"/>
+      <c r="F194" s="1"/>
+      <c r="G194" s="1"/>
+      <c r="H194" s="1"/>
+      <c r="I194" s="1"/>
+      <c r="J194" s="1"/>
+      <c r="L194" s="1"/>
+    </row>
+    <row r="195" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A195" s="1"/>
+      <c r="B195" s="1"/>
+      <c r="C195" s="1"/>
+      <c r="D195" s="1"/>
+      <c r="E195" s="1"/>
+      <c r="F195" s="1"/>
+      <c r="G195" s="1"/>
+      <c r="H195" s="1"/>
+      <c r="I195" s="1"/>
+      <c r="J195" s="1"/>
+      <c r="L195" s="1"/>
+    </row>
+    <row r="196" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A196" s="1"/>
+      <c r="B196" s="1"/>
+      <c r="C196" s="1"/>
+      <c r="D196" s="1"/>
+      <c r="E196" s="1"/>
+      <c r="F196" s="1"/>
+      <c r="G196" s="1"/>
+      <c r="H196" s="1"/>
+      <c r="I196" s="1"/>
+      <c r="J196" s="1"/>
+      <c r="L196" s="1"/>
+    </row>
+    <row r="197" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A197" s="1"/>
+      <c r="B197" s="1"/>
+      <c r="C197" s="1"/>
+      <c r="D197" s="1"/>
+      <c r="E197" s="1"/>
+      <c r="F197" s="1"/>
+      <c r="G197" s="1"/>
+      <c r="H197" s="1"/>
+      <c r="I197" s="1"/>
+      <c r="J197" s="1"/>
+      <c r="L197" s="1"/>
+    </row>
+    <row r="198" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A198" s="1"/>
+      <c r="B198" s="1"/>
+      <c r="C198" s="1"/>
+      <c r="D198" s="1"/>
+      <c r="E198" s="1"/>
+      <c r="F198" s="1"/>
+      <c r="G198" s="1"/>
+      <c r="H198" s="1"/>
+      <c r="I198" s="1"/>
+      <c r="J198" s="1"/>
+      <c r="L198" s="1"/>
+    </row>
+    <row r="199" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A199" s="1"/>
+      <c r="B199" s="1"/>
+      <c r="C199" s="1"/>
+      <c r="D199" s="1"/>
+      <c r="E199" s="1"/>
+      <c r="F199" s="1"/>
+      <c r="G199" s="1"/>
+      <c r="H199" s="1"/>
+      <c r="I199" s="1"/>
+      <c r="J199" s="1"/>
+      <c r="L199" s="1"/>
+    </row>
+    <row r="200" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A200" s="1"/>
+      <c r="B200" s="1"/>
+      <c r="C200" s="1"/>
+      <c r="D200" s="1"/>
+      <c r="E200" s="1"/>
+      <c r="F200" s="1"/>
+      <c r="G200" s="1"/>
+      <c r="H200" s="1"/>
+      <c r="I200" s="1"/>
+      <c r="J200" s="1"/>
+      <c r="L200" s="1"/>
+    </row>
+    <row r="201" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A201" s="1"/>
+      <c r="B201" s="1"/>
+      <c r="C201" s="1"/>
+      <c r="D201" s="1"/>
+      <c r="E201" s="1"/>
+      <c r="F201" s="1"/>
+      <c r="G201" s="1"/>
+      <c r="H201" s="1"/>
+      <c r="I201" s="1"/>
+      <c r="J201" s="1"/>
+      <c r="L201" s="1"/>
+    </row>
+    <row r="202" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A202" s="1"/>
+      <c r="B202" s="1"/>
+      <c r="C202" s="1"/>
+      <c r="D202" s="1"/>
+      <c r="E202" s="1"/>
+      <c r="F202" s="1"/>
+      <c r="G202" s="1"/>
+      <c r="H202" s="1"/>
+      <c r="I202" s="1"/>
+      <c r="J202" s="1"/>
+      <c r="L202" s="1"/>
+    </row>
+    <row r="203" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A203" s="1"/>
+      <c r="B203" s="1"/>
+      <c r="C203" s="1"/>
+      <c r="D203" s="1"/>
+      <c r="E203" s="1"/>
+      <c r="F203" s="1"/>
+      <c r="G203" s="1"/>
+      <c r="H203" s="1"/>
+      <c r="I203" s="1"/>
+      <c r="J203" s="1"/>
+      <c r="L203" s="1"/>
+    </row>
+    <row r="204" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A204" s="1"/>
+      <c r="B204" s="1"/>
+      <c r="C204" s="1"/>
+      <c r="D204" s="1"/>
+      <c r="E204" s="1"/>
+      <c r="F204" s="1"/>
+      <c r="G204" s="1"/>
+      <c r="H204" s="1"/>
+      <c r="I204" s="1"/>
+      <c r="J204" s="1"/>
+      <c r="L204" s="1"/>
+    </row>
+    <row r="205" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A205" s="1"/>
+      <c r="B205" s="1"/>
+      <c r="C205" s="1"/>
+      <c r="D205" s="1"/>
+      <c r="E205" s="1"/>
+      <c r="F205" s="1"/>
+      <c r="G205" s="1"/>
+      <c r="H205" s="1"/>
+      <c r="I205" s="1"/>
+      <c r="J205" s="1"/>
+      <c r="L205" s="1"/>
+    </row>
+    <row r="206" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A206" s="1"/>
+      <c r="B206" s="1"/>
+      <c r="C206" s="1"/>
+      <c r="D206" s="1"/>
+      <c r="E206" s="1"/>
+      <c r="F206" s="1"/>
+      <c r="G206" s="1"/>
+      <c r="H206" s="1"/>
+      <c r="I206" s="1"/>
+      <c r="J206" s="1"/>
+      <c r="L206" s="1"/>
+    </row>
+    <row r="207" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A207" s="1"/>
+      <c r="B207" s="1"/>
+      <c r="C207" s="1"/>
+      <c r="D207" s="1"/>
+      <c r="E207" s="1"/>
+      <c r="F207" s="1"/>
+      <c r="G207" s="1"/>
+      <c r="H207" s="1"/>
+      <c r="I207" s="1"/>
+      <c r="J207" s="1"/>
+      <c r="L207" s="1"/>
+    </row>
+    <row r="208" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A208" s="1"/>
+      <c r="B208" s="1"/>
+      <c r="C208" s="1"/>
+      <c r="D208" s="1"/>
+      <c r="E208" s="1"/>
+      <c r="F208" s="1"/>
+      <c r="G208" s="1"/>
+      <c r="H208" s="1"/>
+      <c r="I208" s="1"/>
+      <c r="J208" s="1"/>
+      <c r="L208" s="1"/>
+    </row>
+    <row r="209" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A209" s="1"/>
+      <c r="B209" s="1"/>
+      <c r="C209" s="1"/>
+      <c r="D209" s="1"/>
+      <c r="E209" s="1"/>
+      <c r="F209" s="1"/>
+      <c r="G209" s="1"/>
+      <c r="H209" s="1"/>
+      <c r="I209" s="1"/>
+      <c r="J209" s="1"/>
+      <c r="L209" s="1"/>
+    </row>
+    <row r="210" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A210" s="1"/>
+      <c r="B210" s="1"/>
+      <c r="C210" s="1"/>
+      <c r="D210" s="1"/>
+      <c r="E210" s="1"/>
+      <c r="F210" s="1"/>
+      <c r="G210" s="1"/>
+      <c r="H210" s="1"/>
+      <c r="I210" s="1"/>
+      <c r="J210" s="1"/>
+      <c r="L210" s="1"/>
+    </row>
+    <row r="211" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A211" s="1"/>
+      <c r="B211" s="1"/>
+      <c r="C211" s="1"/>
+      <c r="D211" s="1"/>
+      <c r="E211" s="1"/>
+      <c r="F211" s="1"/>
+      <c r="G211" s="1"/>
+      <c r="H211" s="1"/>
+      <c r="I211" s="1"/>
+      <c r="J211" s="1"/>
+      <c r="L211" s="1"/>
+    </row>
+    <row r="212" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A212" s="1"/>
+      <c r="B212" s="1"/>
+      <c r="C212" s="1"/>
+      <c r="D212" s="1"/>
+      <c r="E212" s="1"/>
+      <c r="F212" s="1"/>
+      <c r="G212" s="1"/>
+      <c r="H212" s="1"/>
+      <c r="I212" s="1"/>
+      <c r="J212" s="1"/>
+      <c r="L212" s="1"/>
+    </row>
+    <row r="213" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A213" s="1"/>
+      <c r="B213" s="1"/>
+      <c r="C213" s="1"/>
+      <c r="D213" s="1"/>
+      <c r="E213" s="1"/>
+      <c r="F213" s="1"/>
+      <c r="G213" s="1"/>
+      <c r="H213" s="1"/>
+      <c r="I213" s="1"/>
+      <c r="J213" s="1"/>
+      <c r="L213" s="1"/>
+    </row>
+    <row r="214" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A214" s="1"/>
+      <c r="B214" s="1"/>
+      <c r="C214" s="1"/>
+      <c r="D214" s="1"/>
+      <c r="E214" s="1"/>
+      <c r="F214" s="1"/>
+      <c r="G214" s="1"/>
+      <c r="H214" s="1"/>
+      <c r="I214" s="1"/>
+      <c r="J214" s="1"/>
+      <c r="L214" s="1"/>
+    </row>
+    <row r="215" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A215" s="1"/>
+      <c r="B215" s="1"/>
+      <c r="C215" s="1"/>
+      <c r="D215" s="1"/>
+      <c r="E215" s="1"/>
+      <c r="F215" s="1"/>
+      <c r="G215" s="1"/>
+      <c r="H215" s="1"/>
+      <c r="I215" s="1"/>
+      <c r="J215" s="1"/>
+      <c r="L215" s="1"/>
+    </row>
+    <row r="216" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A216" s="1"/>
+      <c r="B216" s="1"/>
+      <c r="C216" s="1"/>
+      <c r="D216" s="1"/>
+      <c r="E216" s="1"/>
+      <c r="F216" s="1"/>
+      <c r="G216" s="1"/>
+      <c r="H216" s="1"/>
+      <c r="I216" s="1"/>
+      <c r="J216" s="1"/>
+      <c r="L216" s="1"/>
+    </row>
+    <row r="217" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A217" s="1"/>
+      <c r="B217" s="1"/>
+      <c r="C217" s="1"/>
+      <c r="D217" s="1"/>
+      <c r="E217" s="1"/>
+      <c r="F217" s="1"/>
+      <c r="G217" s="1"/>
+      <c r="H217" s="1"/>
+      <c r="I217" s="1"/>
+      <c r="J217" s="1"/>
+      <c r="L217" s="1"/>
+    </row>
+    <row r="218" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A218" s="1"/>
+      <c r="B218" s="1"/>
+      <c r="C218" s="1"/>
+      <c r="D218" s="1"/>
+      <c r="E218" s="1"/>
+      <c r="F218" s="1"/>
+      <c r="G218" s="1"/>
+      <c r="H218" s="1"/>
+      <c r="I218" s="1"/>
+      <c r="J218" s="1"/>
+      <c r="L218" s="1"/>
+    </row>
+    <row r="219" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A219" s="1"/>
+      <c r="B219" s="1"/>
+      <c r="C219" s="1"/>
+      <c r="D219" s="1"/>
+      <c r="E219" s="1"/>
+      <c r="F219" s="1"/>
+      <c r="G219" s="1"/>
+      <c r="H219" s="1"/>
+      <c r="I219" s="1"/>
+      <c r="J219" s="1"/>
+      <c r="L219" s="1"/>
+    </row>
+    <row r="220" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A220" s="1"/>
+      <c r="B220" s="1"/>
+      <c r="C220" s="1"/>
+      <c r="D220" s="1"/>
+      <c r="E220" s="1"/>
+      <c r="F220" s="1"/>
+      <c r="G220" s="1"/>
+      <c r="H220" s="1"/>
+      <c r="I220" s="1"/>
+      <c r="J220" s="1"/>
+      <c r="L220" s="1"/>
+    </row>
+    <row r="221" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A221" s="1"/>
+      <c r="B221" s="1"/>
+      <c r="C221" s="1"/>
+      <c r="D221" s="1"/>
+      <c r="E221" s="1"/>
+      <c r="F221" s="1"/>
+      <c r="G221" s="1"/>
+      <c r="H221" s="1"/>
+      <c r="I221" s="1"/>
+      <c r="J221" s="1"/>
+      <c r="L221" s="1"/>
+    </row>
+    <row r="222" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A222" s="1"/>
+      <c r="B222" s="1"/>
+      <c r="C222" s="1"/>
+      <c r="D222" s="1"/>
+      <c r="E222" s="1"/>
+      <c r="F222" s="1"/>
+      <c r="G222" s="1"/>
+      <c r="H222" s="1"/>
+      <c r="I222" s="1"/>
+      <c r="J222" s="1"/>
+      <c r="L222" s="1"/>
+    </row>
+    <row r="223" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A223" s="1"/>
+      <c r="B223" s="1"/>
+      <c r="C223" s="1"/>
+      <c r="D223" s="1"/>
+      <c r="E223" s="1"/>
+      <c r="F223" s="1"/>
+      <c r="G223" s="1"/>
+      <c r="H223" s="1"/>
+      <c r="I223" s="1"/>
+      <c r="J223" s="1"/>
+      <c r="L223" s="1"/>
+    </row>
+    <row r="224" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A224" s="1"/>
+      <c r="B224" s="1"/>
+      <c r="C224" s="1"/>
+      <c r="D224" s="1"/>
+      <c r="E224" s="1"/>
+      <c r="F224" s="1"/>
+      <c r="G224" s="1"/>
+      <c r="H224" s="1"/>
+      <c r="I224" s="1"/>
+      <c r="J224" s="1"/>
+      <c r="L224" s="1"/>
+    </row>
+    <row r="225" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A225" s="1"/>
+      <c r="B225" s="1"/>
+      <c r="C225" s="1"/>
+      <c r="D225" s="1"/>
+      <c r="E225" s="1"/>
+      <c r="F225" s="1"/>
+      <c r="G225" s="1"/>
+      <c r="H225" s="1"/>
+      <c r="I225" s="1"/>
+      <c r="J225" s="1"/>
+      <c r="L225" s="1"/>
+    </row>
+    <row r="226" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A226" s="1"/>
+      <c r="B226" s="1"/>
+      <c r="C226" s="1"/>
+      <c r="D226" s="1"/>
+      <c r="E226" s="1"/>
+      <c r="F226" s="1"/>
+      <c r="G226" s="1"/>
+      <c r="H226" s="1"/>
+      <c r="I226" s="1"/>
+      <c r="J226" s="1"/>
+      <c r="L226" s="1"/>
+    </row>
+    <row r="227" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A227" s="1"/>
+      <c r="B227" s="1"/>
+      <c r="C227" s="1"/>
+      <c r="D227" s="1"/>
+      <c r="E227" s="1"/>
+      <c r="F227" s="1"/>
+      <c r="G227" s="1"/>
+      <c r="H227" s="1"/>
+      <c r="I227" s="1"/>
+      <c r="J227" s="1"/>
+      <c r="L227" s="1"/>
+    </row>
+    <row r="228" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A228" s="1"/>
+      <c r="B228" s="1"/>
+      <c r="C228" s="1"/>
+      <c r="D228" s="1"/>
+      <c r="E228" s="1"/>
+      <c r="F228" s="1"/>
+      <c r="G228" s="1"/>
+      <c r="H228" s="1"/>
+      <c r="I228" s="1"/>
+      <c r="J228" s="1"/>
+      <c r="L228" s="1"/>
+    </row>
+    <row r="229" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A229" s="1"/>
+      <c r="B229" s="1"/>
+      <c r="C229" s="1"/>
+      <c r="D229" s="1"/>
+      <c r="E229" s="1"/>
+      <c r="F229" s="1"/>
+      <c r="G229" s="1"/>
+      <c r="H229" s="1"/>
+      <c r="I229" s="1"/>
+      <c r="J229" s="1"/>
+      <c r="L229" s="1"/>
+    </row>
+    <row r="230" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A230" s="1"/>
+      <c r="B230" s="1"/>
+      <c r="C230" s="1"/>
+      <c r="D230" s="1"/>
+      <c r="E230" s="1"/>
+      <c r="F230" s="1"/>
+      <c r="G230" s="1"/>
+      <c r="H230" s="1"/>
+      <c r="I230" s="1"/>
+      <c r="J230" s="1"/>
+      <c r="L230" s="1"/>
+    </row>
+    <row r="231" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A231" s="1"/>
+      <c r="B231" s="1"/>
+      <c r="C231" s="1"/>
+      <c r="D231" s="1"/>
+      <c r="E231" s="1"/>
+      <c r="F231" s="1"/>
+      <c r="G231" s="1"/>
+      <c r="H231" s="1"/>
+      <c r="I231" s="1"/>
+      <c r="J231" s="1"/>
+      <c r="L231" s="1"/>
+    </row>
+    <row r="232" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A232" s="1"/>
+      <c r="B232" s="1"/>
+      <c r="C232" s="1"/>
+      <c r="D232" s="1"/>
+      <c r="E232" s="1"/>
+      <c r="F232" s="1"/>
+      <c r="G232" s="1"/>
+      <c r="H232" s="1"/>
+      <c r="I232" s="1"/>
+      <c r="J232" s="1"/>
+      <c r="L232" s="1"/>
+    </row>
+    <row r="233" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A233" s="1"/>
+      <c r="B233" s="1"/>
+      <c r="C233" s="1"/>
+      <c r="D233" s="1"/>
+      <c r="E233" s="1"/>
+      <c r="F233" s="1"/>
+      <c r="G233" s="1"/>
+      <c r="H233" s="1"/>
+      <c r="I233" s="1"/>
+      <c r="J233" s="1"/>
+      <c r="L233" s="1"/>
+    </row>
+    <row r="234" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A234" s="1"/>
+      <c r="B234" s="1"/>
+      <c r="C234" s="1"/>
+      <c r="D234" s="1"/>
+      <c r="E234" s="1"/>
+      <c r="F234" s="1"/>
+      <c r="G234" s="1"/>
+      <c r="H234" s="1"/>
+      <c r="I234" s="1"/>
+      <c r="J234" s="1"/>
+      <c r="L234" s="1"/>
+    </row>
+    <row r="235" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A235" s="1"/>
+      <c r="B235" s="1"/>
+      <c r="C235" s="1"/>
+      <c r="D235" s="1"/>
+      <c r="E235" s="1"/>
+      <c r="F235" s="1"/>
+      <c r="G235" s="1"/>
+      <c r="H235" s="1"/>
+      <c r="I235" s="1"/>
+      <c r="J235" s="1"/>
+      <c r="L235" s="1"/>
+    </row>
+    <row r="236" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A236" s="1"/>
+      <c r="B236" s="1"/>
+      <c r="C236" s="1"/>
+      <c r="D236" s="1"/>
+      <c r="E236" s="1"/>
+      <c r="F236" s="1"/>
+      <c r="G236" s="1"/>
+      <c r="H236" s="1"/>
+      <c r="I236" s="1"/>
+      <c r="J236" s="1"/>
+      <c r="L236" s="1"/>
+    </row>
+    <row r="237" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A237" s="1"/>
+      <c r="B237" s="1"/>
+      <c r="C237" s="1"/>
+      <c r="D237" s="1"/>
+      <c r="E237" s="1"/>
+      <c r="F237" s="1"/>
+      <c r="G237" s="1"/>
+      <c r="H237" s="1"/>
+      <c r="I237" s="1"/>
+      <c r="J237" s="1"/>
+      <c r="L237" s="1"/>
+    </row>
+    <row r="238" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A238" s="1"/>
+      <c r="B238" s="1"/>
+      <c r="C238" s="1"/>
+      <c r="D238" s="1"/>
+      <c r="E238" s="1"/>
+      <c r="F238" s="1"/>
+      <c r="G238" s="1"/>
+      <c r="H238" s="1"/>
+      <c r="I238" s="1"/>
+      <c r="J238" s="1"/>
+      <c r="L238" s="1"/>
+    </row>
+    <row r="239" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A239" s="1"/>
+      <c r="B239" s="1"/>
+      <c r="C239" s="1"/>
+      <c r="D239" s="1"/>
+      <c r="E239" s="1"/>
+      <c r="F239" s="1"/>
+      <c r="G239" s="1"/>
+      <c r="H239" s="1"/>
+      <c r="I239" s="1"/>
+      <c r="J239" s="1"/>
+      <c r="L239" s="1"/>
+    </row>
+    <row r="240" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A240" s="1"/>
+      <c r="B240" s="1"/>
+      <c r="C240" s="1"/>
+      <c r="D240" s="1"/>
+      <c r="E240" s="1"/>
+      <c r="F240" s="1"/>
+      <c r="G240" s="1"/>
+      <c r="H240" s="1"/>
+      <c r="I240" s="1"/>
+      <c r="J240" s="1"/>
+      <c r="L240" s="1"/>
+    </row>
+    <row r="241" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A241" s="1"/>
+      <c r="B241" s="1"/>
+      <c r="C241" s="1"/>
+      <c r="D241" s="1"/>
+      <c r="E241" s="1"/>
+      <c r="F241" s="1"/>
+      <c r="G241" s="1"/>
+      <c r="H241" s="1"/>
+      <c r="I241" s="1"/>
+      <c r="J241" s="1"/>
+      <c r="L241" s="1"/>
+    </row>
+    <row r="242" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A242" s="1"/>
+      <c r="B242" s="1"/>
+      <c r="C242" s="1"/>
+      <c r="D242" s="1"/>
+      <c r="E242" s="1"/>
+      <c r="F242" s="1"/>
+      <c r="G242" s="1"/>
+      <c r="H242" s="1"/>
+      <c r="I242" s="1"/>
+      <c r="J242" s="1"/>
+      <c r="L242" s="1"/>
+    </row>
+    <row r="243" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A243" s="1"/>
+      <c r="B243" s="1"/>
+      <c r="C243" s="1"/>
+      <c r="D243" s="1"/>
+      <c r="E243" s="1"/>
+      <c r="F243" s="1"/>
+      <c r="G243" s="1"/>
+      <c r="H243" s="1"/>
+      <c r="I243" s="1"/>
+      <c r="J243" s="1"/>
+      <c r="L243" s="1"/>
+    </row>
+    <row r="244" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A244" s="1"/>
+      <c r="B244" s="1"/>
+      <c r="C244" s="1"/>
+      <c r="D244" s="1"/>
+      <c r="E244" s="1"/>
+      <c r="F244" s="1"/>
+      <c r="G244" s="1"/>
+      <c r="H244" s="1"/>
+      <c r="I244" s="1"/>
+      <c r="J244" s="1"/>
+      <c r="L244" s="1"/>
+    </row>
+    <row r="245" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A245" s="1"/>
+      <c r="B245" s="1"/>
+      <c r="C245" s="1"/>
+      <c r="D245" s="1"/>
+      <c r="E245" s="1"/>
+      <c r="F245" s="1"/>
+      <c r="G245" s="1"/>
+      <c r="H245" s="1"/>
+      <c r="I245" s="1"/>
+      <c r="J245" s="1"/>
+      <c r="L245" s="1"/>
+    </row>
+    <row r="246" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A246" s="1"/>
+      <c r="B246" s="1"/>
+      <c r="C246" s="1"/>
+      <c r="D246" s="1"/>
+      <c r="E246" s="1"/>
+      <c r="F246" s="1"/>
+      <c r="G246" s="1"/>
+      <c r="H246" s="1"/>
+      <c r="I246" s="1"/>
+      <c r="J246" s="1"/>
+      <c r="L246" s="1"/>
+    </row>
+    <row r="247" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A247" s="1"/>
+      <c r="B247" s="1"/>
+      <c r="C247" s="1"/>
+      <c r="D247" s="1"/>
+      <c r="E247" s="1"/>
+      <c r="F247" s="1"/>
+      <c r="G247" s="1"/>
+      <c r="H247" s="1"/>
+      <c r="I247" s="1"/>
+      <c r="J247" s="1"/>
+      <c r="L247" s="1"/>
+    </row>
+    <row r="248" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A248" s="1"/>
+      <c r="B248" s="1"/>
+      <c r="C248" s="1"/>
+      <c r="D248" s="1"/>
+      <c r="E248" s="1"/>
+      <c r="F248" s="1"/>
+      <c r="G248" s="1"/>
+      <c r="H248" s="1"/>
+      <c r="I248" s="1"/>
+      <c r="J248" s="1"/>
+      <c r="L248" s="1"/>
+    </row>
+    <row r="249" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A249" s="1"/>
+      <c r="B249" s="1"/>
+      <c r="C249" s="1"/>
+      <c r="D249" s="1"/>
+      <c r="E249" s="1"/>
+      <c r="F249" s="1"/>
+      <c r="G249" s="1"/>
+      <c r="H249" s="1"/>
+      <c r="I249" s="1"/>
+      <c r="J249" s="1"/>
+      <c r="L249" s="1"/>
+    </row>
+    <row r="250" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A250" s="1"/>
+      <c r="B250" s="1"/>
+      <c r="C250" s="1"/>
+      <c r="D250" s="1"/>
+      <c r="E250" s="1"/>
+      <c r="F250" s="1"/>
+      <c r="G250" s="1"/>
+      <c r="H250" s="1"/>
+      <c r="I250" s="1"/>
+      <c r="J250" s="1"/>
+      <c r="L250" s="1"/>
+    </row>
+    <row r="251" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A251" s="1"/>
+      <c r="B251" s="1"/>
+      <c r="C251" s="1"/>
+      <c r="D251" s="1"/>
+      <c r="E251" s="1"/>
+      <c r="F251" s="1"/>
+      <c r="G251" s="1"/>
+      <c r="H251" s="1"/>
+      <c r="I251" s="1"/>
+      <c r="J251" s="1"/>
+      <c r="L251" s="1"/>
+    </row>
+    <row r="252" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A252" s="1"/>
+      <c r="B252" s="1"/>
+      <c r="C252" s="1"/>
+      <c r="D252" s="1"/>
+      <c r="E252" s="1"/>
+      <c r="F252" s="1"/>
+      <c r="G252" s="1"/>
+      <c r="H252" s="1"/>
+      <c r="I252" s="1"/>
+      <c r="J252" s="1"/>
+      <c r="L252" s="1"/>
+    </row>
+    <row r="253" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A253" s="1"/>
+      <c r="B253" s="1"/>
+      <c r="C253" s="1"/>
+      <c r="D253" s="1"/>
+      <c r="E253" s="1"/>
+      <c r="F253" s="1"/>
+      <c r="G253" s="1"/>
+      <c r="H253" s="1"/>
+      <c r="I253" s="1"/>
+      <c r="J253" s="1"/>
+      <c r="L253" s="1"/>
+    </row>
+    <row r="254" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A254" s="1"/>
+      <c r="B254" s="1"/>
+      <c r="C254" s="1"/>
+      <c r="D254" s="1"/>
+      <c r="E254" s="1"/>
+      <c r="F254" s="1"/>
+      <c r="G254" s="1"/>
+      <c r="H254" s="1"/>
+      <c r="I254" s="1"/>
+      <c r="J254" s="1"/>
+      <c r="L254" s="1"/>
+    </row>
+    <row r="255" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A255" s="1"/>
+      <c r="B255" s="1"/>
+      <c r="C255" s="1"/>
+      <c r="D255" s="1"/>
+      <c r="E255" s="1"/>
+      <c r="F255" s="1"/>
+      <c r="G255" s="1"/>
+      <c r="H255" s="1"/>
+      <c r="I255" s="1"/>
+      <c r="J255" s="1"/>
+      <c r="L255" s="1"/>
+    </row>
+    <row r="256" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A256" s="1"/>
+      <c r="B256" s="1"/>
+      <c r="C256" s="1"/>
+      <c r="D256" s="1"/>
+      <c r="E256" s="1"/>
+      <c r="F256" s="1"/>
+      <c r="G256" s="1"/>
+      <c r="H256" s="1"/>
+      <c r="I256" s="1"/>
+      <c r="J256" s="1"/>
+      <c r="L256" s="1"/>
+    </row>
+    <row r="257" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A257" s="1"/>
+      <c r="B257" s="1"/>
+      <c r="C257" s="1"/>
+      <c r="D257" s="1"/>
+      <c r="E257" s="1"/>
+      <c r="F257" s="1"/>
+      <c r="G257" s="1"/>
+      <c r="H257" s="1"/>
+      <c r="I257" s="1"/>
+      <c r="J257" s="1"/>
+      <c r="L257" s="1"/>
+    </row>
+    <row r="258" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A258" s="1"/>
+      <c r="B258" s="1"/>
+      <c r="C258" s="1"/>
+      <c r="D258" s="1"/>
+      <c r="E258" s="1"/>
+      <c r="F258" s="1"/>
+      <c r="G258" s="1"/>
+      <c r="H258" s="1"/>
+      <c r="I258" s="1"/>
+      <c r="J258" s="1"/>
+      <c r="L258" s="1"/>
+    </row>
+    <row r="259" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A259" s="1"/>
+      <c r="B259" s="1"/>
+      <c r="C259" s="1"/>
+      <c r="D259" s="1"/>
+      <c r="E259" s="1"/>
+      <c r="F259" s="1"/>
+      <c r="G259" s="1"/>
+      <c r="H259" s="1"/>
+      <c r="I259" s="1"/>
+      <c r="J259" s="1"/>
+      <c r="L259" s="1"/>
+    </row>
+    <row r="260" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A260" s="1"/>
+      <c r="B260" s="1"/>
+      <c r="C260" s="1"/>
+      <c r="D260" s="1"/>
+      <c r="E260" s="1"/>
+      <c r="F260" s="1"/>
+      <c r="G260" s="1"/>
+      <c r="H260" s="1"/>
+      <c r="I260" s="1"/>
+      <c r="J260" s="1"/>
+      <c r="L260" s="1"/>
+    </row>
+    <row r="261" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A261" s="1"/>
+      <c r="B261" s="1"/>
+      <c r="C261" s="1"/>
+      <c r="D261" s="1"/>
+      <c r="E261" s="1"/>
+      <c r="F261" s="1"/>
+      <c r="G261" s="1"/>
+      <c r="H261" s="1"/>
+      <c r="I261" s="1"/>
+      <c r="J261" s="1"/>
+      <c r="L261" s="1"/>
+    </row>
+    <row r="262" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A262" s="1"/>
+      <c r="B262" s="1"/>
+      <c r="C262" s="1"/>
+      <c r="D262" s="1"/>
+      <c r="E262" s="1"/>
+      <c r="F262" s="1"/>
+      <c r="G262" s="1"/>
+      <c r="H262" s="1"/>
+      <c r="I262" s="1"/>
+      <c r="J262" s="1"/>
+      <c r="L262" s="1"/>
+    </row>
+    <row r="263" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A263" s="1"/>
+      <c r="B263" s="1"/>
+      <c r="C263" s="1"/>
+      <c r="D263" s="1"/>
+      <c r="E263" s="1"/>
+      <c r="F263" s="1"/>
+      <c r="G263" s="1"/>
+      <c r="H263" s="1"/>
+      <c r="I263" s="1"/>
+      <c r="J263" s="1"/>
+      <c r="L263" s="1"/>
+    </row>
+    <row r="264" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A264" s="1"/>
+      <c r="B264" s="1"/>
+      <c r="C264" s="1"/>
+      <c r="D264" s="1"/>
+      <c r="E264" s="1"/>
+      <c r="F264" s="1"/>
+      <c r="G264" s="1"/>
+      <c r="H264" s="1"/>
+      <c r="I264" s="1"/>
+      <c r="J264" s="1"/>
+      <c r="L264" s="1"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>